--- a/ClearOps_Database_Mapped.xlsx
+++ b/ClearOps_Database_Mapped.xlsx
@@ -14,10 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues_Fixed" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Table_Catalog'!$A$1:$E$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Columns_Corrected'!$A$1:$G$388</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Table_Catalog'!$A$1:$E$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Columns_Corrected'!$A$1:$G$387</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'FK_Mapping'!$A$1:$F$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Issues_Fixed'!$A$1:$D$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Issues_Fixed'!$A$1:$D$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,14 +493,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: 28 tables across 4 groups (Setup 7, TimePlanner 3, Project 7, Admin 11).</t>
+          <t>Source (latest upload): 27 tables across 4 groups (Setup 7, TimePlanner 3, Project 6, Admin 11). Compared with the previous upload, the only change is that ProjectManualCreation was removed; every other table is identical.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Result: 33 tables in the corrected model = 25 kept/fixed + 5 new + 3 retired (merged).</t>
+          <t>Result: 32 tables in the corrected model = 25 kept/fixed + 5 new + 2 to retire (still in your file; ProjectManualCreation is already gone).</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>3. Duplicate tables: ProjectManualCreation duplicated Project_Master; RolesandPermissions duplicated Role/Page/Permission/Users; ProjectForecasting duplicated ProjectSTP. All retired/merged.</t>
+          <t>3. Duplicate tables: ProjectManualCreation (now removed from your file, good) duplicated Project_Master, so manual creation is covered by Project_Master.Source; RolesandPermissions duplicated Role/Page/Permission/Users; ProjectForecasting duplicated ProjectSTP. ProjectForecasting and RolesandPermissions are still in your file and should be retired.</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1249,30 +1249,34 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ProjectManualCreation</t>
+          <t>Admin_IntegrationStatus</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Merged</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Sys_Integration_Id</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>RETIRED: field-for-field duplicate of Project_Master. Use Project_Master.Source='MANUAL'</t>
+          <t>Integration status per source system</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Admin_IntegrationStatus</t>
+          <t>ClearOps_Logs</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1287,19 +1291,19 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Sys_Integration_Id</t>
+          <t>Log_Id</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Integration status per source system</t>
+          <t>Integration/cron run log (was Logs_table)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Logs</t>
+          <t>ClearOps_Role</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1314,19 +1318,19 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Log_Id</t>
+          <t>Role_Id</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Integration/cron run log (was Logs_table)</t>
+          <t>Role master</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Role</t>
+          <t>ClearOps_Page</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1341,19 +1345,19 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Role_Id</t>
+          <t>Page_Id</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Role master</t>
+          <t>Application pages/screens</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Page</t>
+          <t>ClearOps_Access</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1368,19 +1372,19 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Page_Id</t>
+          <t>Access_Id</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Application pages/screens</t>
+          <t>Access level lookup: None / R / R/W</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Access</t>
+          <t>ClearOps_Permission</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1395,19 +1399,19 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Access_Id</t>
+          <t>Permission_Id</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Access level lookup: None / R / R/W</t>
+          <t>Role x Page -&gt; access level (mapping table)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Permission</t>
+          <t>ClearOps_Users</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1422,19 +1426,19 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Permission_Id</t>
+          <t>User_Id</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Role x Page -&gt; access level (mapping table)</t>
+          <t>Application users</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Users</t>
+          <t>ClearOps_Login</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1449,19 +1453,19 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>User_Id</t>
+          <t>Login_Id</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Application users</t>
+          <t>SSO identity mapping</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Login</t>
+          <t>ClearOps_UserLogin</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1476,19 +1480,19 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Login_Id</t>
+          <t>User_Login_Id</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>SSO identity mapping</t>
+          <t>Login event history</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_UserLogin</t>
+          <t>RolesandPermissions</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1496,47 +1500,20 @@
           <t>Admin</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>User_Login_Id</t>
-        </is>
-      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Merged</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Login event history</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>RolesandPermissions</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Merged</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
           <t>RETIRED: denormalised sheet of Role+Page+Permission+Users. Replace with a VIEW</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E34"/>
+  <autoFilter ref="A1:E33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1547,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G388"/>
+  <dimension ref="A1:G387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10358,27 +10335,31 @@
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>ProjectManualCreation</t>
+          <t>Admin_IntegrationStatus</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>All columns</t>
-        </is>
-      </c>
-      <c r="C313" s="2" t="inlineStr"/>
-      <c r="D313" s="2" t="inlineStr"/>
+          <t>Sys_Integration_Id</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E313" s="2" t="inlineStr"/>
-      <c r="F313" s="7" t="inlineStr">
-        <is>
-          <t>Moved/Removed</t>
-        </is>
-      </c>
-      <c r="G313" s="2" t="inlineStr">
-        <is>
-          <t>Duplicate of Project_Master</t>
-        </is>
-      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>Kept</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -10388,26 +10369,26 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Sys_Integration_Id</t>
+          <t>System_Name</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D314" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr"/>
       <c r="E314" s="2" t="inlineStr"/>
-      <c r="F314" s="2" t="inlineStr">
-        <is>
-          <t>Kept</t>
-        </is>
-      </c>
-      <c r="G314" s="2" t="inlineStr"/>
+      <c r="F314" s="5" t="inlineStr">
+        <is>
+          <t>Renamed</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>Was System</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -10417,26 +10398,22 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>System_Name</t>
+          <t>Last_Sync_DateTime</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>DATETIME2</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr"/>
       <c r="E315" s="2" t="inlineStr"/>
-      <c r="F315" s="5" t="inlineStr">
-        <is>
-          <t>Renamed</t>
-        </is>
-      </c>
-      <c r="G315" s="2" t="inlineStr">
-        <is>
-          <t>Was System</t>
-        </is>
-      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>Kept</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -10446,12 +10423,12 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Last_Sync_DateTime</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr"/>
@@ -10471,22 +10448,26 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Records_Captured</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr"/>
       <c r="E317" s="2" t="inlineStr"/>
-      <c r="F317" s="2" t="inlineStr">
-        <is>
-          <t>Kept</t>
-        </is>
-      </c>
-      <c r="G317" s="2" t="inlineStr"/>
+      <c r="F317" s="5" t="inlineStr">
+        <is>
+          <t>Renamed</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>Was record_captured</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -10496,24 +10477,24 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Records_Captured</t>
+          <t>Created_By</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr"/>
       <c r="E318" s="2" t="inlineStr"/>
-      <c r="F318" s="5" t="inlineStr">
-        <is>
-          <t>Renamed</t>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>Kept</t>
         </is>
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>Was record_captured</t>
+          <t>Audit column</t>
         </is>
       </c>
     </row>
@@ -10525,12 +10506,12 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Created_By</t>
+          <t>Created_Date</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>DATETIME2</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr"/>
@@ -10554,12 +10535,12 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Created_Date</t>
+          <t>Modified_By</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr"/>
@@ -10583,12 +10564,12 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>Modified_By</t>
+          <t>Modified_Date</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>DATETIME2</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr"/>
@@ -10607,31 +10588,31 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>Admin_IntegrationStatus</t>
+          <t>ClearOps_Logs</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>Modified_Date</t>
+          <t>Log_Id</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
-        </is>
-      </c>
-      <c r="D322" s="2" t="inlineStr"/>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E322" s="2" t="inlineStr"/>
       <c r="F322" s="2" t="inlineStr">
         <is>
           <t>Kept</t>
         </is>
       </c>
-      <c r="G322" s="2" t="inlineStr">
-        <is>
-          <t>Audit column</t>
-        </is>
-      </c>
+      <c r="G322" s="2" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -10641,7 +10622,7 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>Log_Id</t>
+          <t>Sys_Integration_Id</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
@@ -10651,10 +10632,14 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E323" s="2" t="inlineStr"/>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>Admin_IntegrationStatus.Sys_Integration_Id</t>
+        </is>
+      </c>
       <c r="F323" s="2" t="inlineStr">
         <is>
           <t>Kept</t>
@@ -10670,30 +10655,26 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>Sys_Integration_Id</t>
+          <t>Cron_Job_Run_Id</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D324" s="2" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E324" s="2" t="inlineStr">
-        <is>
-          <t>Admin_IntegrationStatus.Sys_Integration_Id</t>
-        </is>
-      </c>
-      <c r="F324" s="2" t="inlineStr">
-        <is>
-          <t>Kept</t>
-        </is>
-      </c>
-      <c r="G324" s="2" t="inlineStr"/>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr"/>
+      <c r="E324" s="2" t="inlineStr"/>
+      <c r="F324" s="5" t="inlineStr">
+        <is>
+          <t>Renamed</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>Was cornjob run_id (typo)</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -10703,24 +10684,24 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>Cron_Job_Run_Id</t>
+          <t>Run_Start</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>DATETIME2</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr"/>
       <c r="E325" s="2" t="inlineStr"/>
-      <c r="F325" s="5" t="inlineStr">
-        <is>
-          <t>Renamed</t>
+      <c r="F325" s="6" t="inlineStr">
+        <is>
+          <t>Added</t>
         </is>
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>Was cornjob run_id (typo)</t>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10713,7 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>Run_Start</t>
+          <t>Run_End</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
@@ -10761,12 +10742,12 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>Run_End</t>
+          <t>Run_Status</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr"/>
@@ -10790,12 +10771,12 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>Run_Status</t>
+          <t>Records_Processed</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr"/>
@@ -10819,12 +10800,12 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>Records_Processed</t>
+          <t>Error_Message</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>VARCHAR(2000)</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr"/>
@@ -10848,12 +10829,12 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>Error_Message</t>
+          <t>Created_By</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(2000)</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr"/>
@@ -10865,7 +10846,7 @@
       </c>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Audit column (MISSING in sheet)</t>
         </is>
       </c>
     </row>
@@ -10877,12 +10858,12 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>Created_By</t>
+          <t>Created_Date</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>DATETIME2</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr"/>
@@ -10906,12 +10887,12 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>Created_Date</t>
+          <t>Modified_By</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr"/>
@@ -10935,12 +10916,12 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>Modified_By</t>
+          <t>Modified_Date</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>DATETIME2</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr"/>
@@ -10959,31 +10940,31 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Logs</t>
+          <t>ClearOps_Role</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>Modified_Date</t>
+          <t>Role_Id</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
-        </is>
-      </c>
-      <c r="D334" s="2" t="inlineStr"/>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E334" s="2" t="inlineStr"/>
-      <c r="F334" s="6" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="G334" s="2" t="inlineStr">
-        <is>
-          <t>Audit column (MISSING in sheet)</t>
-        </is>
-      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>Kept</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -10993,19 +10974,15 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>Role_Id</t>
+          <t>Role_Name</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D335" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr"/>
       <c r="E335" s="2" t="inlineStr"/>
       <c r="F335" s="2" t="inlineStr">
         <is>
@@ -11022,12 +10999,12 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>Role_Name</t>
+          <t>Role_Type</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>VARCHAR(30)</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr"/>
@@ -11047,22 +11024,26 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>Role_Type</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr"/>
       <c r="E337" s="2" t="inlineStr"/>
-      <c r="F337" s="2" t="inlineStr">
-        <is>
-          <t>Kept</t>
-        </is>
-      </c>
-      <c r="G337" s="2" t="inlineStr"/>
+      <c r="F337" s="6" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>From RolesandPermissions</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -11072,24 +11053,24 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Created_By</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr"/>
       <c r="E338" s="2" t="inlineStr"/>
-      <c r="F338" s="6" t="inlineStr">
-        <is>
-          <t>Added</t>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>Kept</t>
         </is>
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>From RolesandPermissions</t>
+          <t>Audit column</t>
         </is>
       </c>
     </row>
@@ -11101,12 +11082,12 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>Created_By</t>
+          <t>Created_Date</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>DATETIME2</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr"/>
@@ -11130,12 +11111,12 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>Created_Date</t>
+          <t>Modified_By</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr"/>
@@ -11159,12 +11140,12 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>Modified_By</t>
+          <t>Modified_Date</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>DATETIME2</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr"/>
@@ -11183,31 +11164,31 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Role</t>
+          <t>ClearOps_Page</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>Modified_Date</t>
+          <t>Page_Id</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
-        </is>
-      </c>
-      <c r="D342" s="2" t="inlineStr"/>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E342" s="2" t="inlineStr"/>
       <c r="F342" s="2" t="inlineStr">
         <is>
           <t>Kept</t>
         </is>
       </c>
-      <c r="G342" s="2" t="inlineStr">
-        <is>
-          <t>Audit column</t>
-        </is>
-      </c>
+      <c r="G342" s="2" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -11217,19 +11198,15 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>Page_Id</t>
+          <t>Page_Number</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D343" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr"/>
       <c r="E343" s="2" t="inlineStr"/>
       <c r="F343" s="2" t="inlineStr">
         <is>
@@ -11246,12 +11223,12 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>Page_Number</t>
+          <t>Page_Name</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>VARCHAR(150)</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr"/>
@@ -11271,22 +11248,26 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>Page_Name</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(150)</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr"/>
       <c r="E345" s="2" t="inlineStr"/>
-      <c r="F345" s="2" t="inlineStr">
-        <is>
-          <t>Kept</t>
-        </is>
-      </c>
-      <c r="G345" s="2" t="inlineStr"/>
+      <c r="F345" s="6" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>Moved from RolesandPermissions</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -11296,7 +11277,7 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Created_By</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
@@ -11306,14 +11287,14 @@
       </c>
       <c r="D346" s="2" t="inlineStr"/>
       <c r="E346" s="2" t="inlineStr"/>
-      <c r="F346" s="6" t="inlineStr">
-        <is>
-          <t>Added</t>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>Kept</t>
         </is>
       </c>
       <c r="G346" s="2" t="inlineStr">
         <is>
-          <t>Moved from RolesandPermissions</t>
+          <t>Audit column</t>
         </is>
       </c>
     </row>
@@ -11325,12 +11306,12 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>Created_By</t>
+          <t>Created_Date</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>DATETIME2</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr"/>
@@ -11354,12 +11335,12 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>Created_Date</t>
+          <t>Modified_By</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr"/>
@@ -11383,12 +11364,12 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>Modified_By</t>
+          <t>Modified_Date</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>DATETIME2</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr"/>
@@ -11407,31 +11388,31 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Page</t>
+          <t>ClearOps_Access</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>Modified_Date</t>
+          <t>Access_Id</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
-        </is>
-      </c>
-      <c r="D350" s="2" t="inlineStr"/>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E350" s="2" t="inlineStr"/>
       <c r="F350" s="2" t="inlineStr">
         <is>
           <t>Kept</t>
         </is>
       </c>
-      <c r="G350" s="2" t="inlineStr">
-        <is>
-          <t>Audit column</t>
-        </is>
-      </c>
+      <c r="G350" s="2" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -11441,26 +11422,26 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>Access_Id</t>
+          <t>Access_Type</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D351" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr"/>
       <c r="E351" s="2" t="inlineStr"/>
-      <c r="F351" s="2" t="inlineStr">
-        <is>
-          <t>Kept</t>
-        </is>
-      </c>
-      <c r="G351" s="2" t="inlineStr"/>
+      <c r="F351" s="5" t="inlineStr">
+        <is>
+          <t>Renamed</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>Was Accrss_type (typo)</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -11470,24 +11451,24 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>Access_Type</t>
+          <t>Created_By</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr"/>
       <c r="E352" s="2" t="inlineStr"/>
-      <c r="F352" s="5" t="inlineStr">
-        <is>
-          <t>Renamed</t>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>Kept</t>
         </is>
       </c>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>Was Accrss_type (typo)</t>
+          <t>Audit column</t>
         </is>
       </c>
     </row>
@@ -11499,12 +11480,12 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>Created_By</t>
+          <t>Created_Date</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>DATETIME2</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr"/>
@@ -11528,12 +11509,12 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>Created_Date</t>
+          <t>Modified_By</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr"/>
@@ -11557,12 +11538,12 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>Modified_By</t>
+          <t>Modified_Date</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>DATETIME2</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr"/>
@@ -11581,31 +11562,31 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Access</t>
+          <t>ClearOps_Permission</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>Modified_Date</t>
+          <t>Permission_Id</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
-        </is>
-      </c>
-      <c r="D356" s="2" t="inlineStr"/>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E356" s="2" t="inlineStr"/>
       <c r="F356" s="2" t="inlineStr">
         <is>
           <t>Kept</t>
         </is>
       </c>
-      <c r="G356" s="2" t="inlineStr">
-        <is>
-          <t>Audit column</t>
-        </is>
-      </c>
+      <c r="G356" s="2" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -11615,7 +11596,7 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>Permission_Id</t>
+          <t>Role_Id</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
@@ -11625,10 +11606,14 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E357" s="2" t="inlineStr"/>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>ClearOps_Role.Role_Id</t>
+        </is>
+      </c>
       <c r="F357" s="2" t="inlineStr">
         <is>
           <t>Kept</t>
@@ -11644,7 +11629,7 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>Role_Id</t>
+          <t>Page_Id</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
@@ -11659,7 +11644,7 @@
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Role.Role_Id</t>
+          <t>ClearOps_Page.Page_Id</t>
         </is>
       </c>
       <c r="F358" s="2" t="inlineStr">
@@ -11677,7 +11662,7 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>Page_Id</t>
+          <t>Access_Id</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
@@ -11692,7 +11677,7 @@
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Page.Page_Id</t>
+          <t>ClearOps_Access.Access_Id</t>
         </is>
       </c>
       <c r="F359" s="2" t="inlineStr">
@@ -11710,30 +11695,22 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>Access_Id</t>
-        </is>
-      </c>
-      <c r="C360" s="2" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D360" s="2" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E360" s="2" t="inlineStr">
-        <is>
-          <t>ClearOps_Access.Access_Id</t>
-        </is>
-      </c>
-      <c r="F360" s="2" t="inlineStr">
-        <is>
-          <t>Kept</t>
-        </is>
-      </c>
-      <c r="G360" s="2" t="inlineStr"/>
+          <t>HRID</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr"/>
+      <c r="D360" s="2" t="inlineStr"/>
+      <c r="E360" s="2" t="inlineStr"/>
+      <c r="F360" s="7" t="inlineStr">
+        <is>
+          <t>Removed</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>A role permission is not per person; user-&gt;role is in ClearOps_Users</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -11743,20 +11720,24 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>HRID</t>
-        </is>
-      </c>
-      <c r="C361" s="2" t="inlineStr"/>
+          <t>Created_By</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
       <c r="D361" s="2" t="inlineStr"/>
       <c r="E361" s="2" t="inlineStr"/>
-      <c r="F361" s="7" t="inlineStr">
-        <is>
-          <t>Removed</t>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>Kept</t>
         </is>
       </c>
       <c r="G361" s="2" t="inlineStr">
         <is>
-          <t>A role permission is not per person; user-&gt;role is in ClearOps_Users</t>
+          <t>Audit column</t>
         </is>
       </c>
     </row>
@@ -11768,12 +11749,12 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>Created_By</t>
+          <t>Created_Date</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>DATETIME2</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr"/>
@@ -11797,12 +11778,12 @@
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>Created_Date</t>
+          <t>Modified_By</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr"/>
@@ -11826,12 +11807,12 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>Modified_By</t>
+          <t>Modified_Date</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>DATETIME2</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr"/>
@@ -11850,29 +11831,33 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Permission</t>
+          <t>ClearOps_Users</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>Modified_Date</t>
+          <t>User_Id</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
-        </is>
-      </c>
-      <c r="D365" s="2" t="inlineStr"/>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E365" s="2" t="inlineStr"/>
-      <c r="F365" s="2" t="inlineStr">
-        <is>
-          <t>Kept</t>
+      <c r="F365" s="5" t="inlineStr">
+        <is>
+          <t>Renamed</t>
         </is>
       </c>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>Audit column</t>
+          <t>Was User_ID(PK) (sr_id)</t>
         </is>
       </c>
     </row>
@@ -11884,28 +11869,32 @@
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>User_Id</t>
+          <t>HRID</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E366" s="2" t="inlineStr"/>
-      <c r="F366" s="5" t="inlineStr">
-        <is>
-          <t>Renamed</t>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>Employee_Master.HRID</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>Kept</t>
         </is>
       </c>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>Was User_ID(PK) (sr_id)</t>
+          <t>UNIQUE</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11906,12 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>HRID</t>
+          <t>Role_Id</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
@@ -11932,7 +11921,7 @@
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>Employee_Master.HRID</t>
+          <t>ClearOps_Role.Role_Id</t>
         </is>
       </c>
       <c r="F367" s="2" t="inlineStr">
@@ -11940,11 +11929,7 @@
           <t>Kept</t>
         </is>
       </c>
-      <c r="G367" s="2" t="inlineStr">
-        <is>
-          <t>UNIQUE</t>
-        </is>
-      </c>
+      <c r="G367" s="2" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -11954,27 +11939,19 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>Role_Id</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D368" s="2" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E368" s="2" t="inlineStr">
-        <is>
-          <t>ClearOps_Role.Role_Id</t>
-        </is>
-      </c>
-      <c r="F368" s="2" t="inlineStr">
-        <is>
-          <t>Kept</t>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr"/>
+      <c r="E368" s="2" t="inlineStr"/>
+      <c r="F368" s="6" t="inlineStr">
+        <is>
+          <t>Added</t>
         </is>
       </c>
       <c r="G368" s="2" t="inlineStr"/>
@@ -11987,22 +11964,22 @@
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="C369" s="2" t="inlineStr">
-        <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
+          <t>Role_Name, Name, Email</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr"/>
       <c r="D369" s="2" t="inlineStr"/>
       <c r="E369" s="2" t="inlineStr"/>
-      <c r="F369" s="6" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="G369" s="2" t="inlineStr"/>
+      <c r="F369" s="7" t="inlineStr">
+        <is>
+          <t>Removed</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>Derivable via Role_Id / HRID</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -12012,20 +11989,24 @@
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>Role_Name, Name, Email</t>
-        </is>
-      </c>
-      <c r="C370" s="2" t="inlineStr"/>
+          <t>Created_By</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
       <c r="D370" s="2" t="inlineStr"/>
       <c r="E370" s="2" t="inlineStr"/>
-      <c r="F370" s="7" t="inlineStr">
-        <is>
-          <t>Removed</t>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>Kept</t>
         </is>
       </c>
       <c r="G370" s="2" t="inlineStr">
         <is>
-          <t>Derivable via Role_Id / HRID</t>
+          <t>Audit column</t>
         </is>
       </c>
     </row>
@@ -12037,12 +12018,12 @@
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>Created_By</t>
+          <t>Created_Date</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>DATETIME2</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr"/>
@@ -12066,12 +12047,12 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>Created_Date</t>
+          <t>Modified_By</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr"/>
@@ -12095,12 +12076,12 @@
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>Modified_By</t>
+          <t>Modified_Date</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>DATETIME2</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr"/>
@@ -12119,29 +12100,33 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Users</t>
+          <t>ClearOps_Login</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>Modified_Date</t>
+          <t>Login_Id</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
-        </is>
-      </c>
-      <c r="D374" s="2" t="inlineStr"/>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E374" s="2" t="inlineStr"/>
-      <c r="F374" s="2" t="inlineStr">
-        <is>
-          <t>Kept</t>
+      <c r="F374" s="6" t="inlineStr">
+        <is>
+          <t>Added</t>
         </is>
       </c>
       <c r="G374" s="2" t="inlineStr">
         <is>
-          <t>Audit column</t>
+          <t>MISSING: table had no PK</t>
         </is>
       </c>
     </row>
@@ -12153,30 +12138,30 @@
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>Login_Id</t>
+          <t>HRID</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E375" s="2" t="inlineStr"/>
-      <c r="F375" s="6" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="G375" s="2" t="inlineStr">
-        <is>
-          <t>MISSING: table had no PK</t>
-        </is>
-      </c>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>Employee_Master.HRID</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>Kept</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -12186,30 +12171,26 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>HRID</t>
+          <t>SSO_Id</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
-      <c r="D376" s="2" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E376" s="2" t="inlineStr">
-        <is>
-          <t>Employee_Master.HRID</t>
-        </is>
-      </c>
-      <c r="F376" s="2" t="inlineStr">
-        <is>
-          <t>Kept</t>
-        </is>
-      </c>
-      <c r="G376" s="2" t="inlineStr"/>
+          <t>VARCHAR(200)</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr"/>
+      <c r="E376" s="2" t="inlineStr"/>
+      <c r="F376" s="5" t="inlineStr">
+        <is>
+          <t>Renamed</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>Was SSO</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -12219,24 +12200,20 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>SSO_Id</t>
-        </is>
-      </c>
-      <c r="C377" s="2" t="inlineStr">
-        <is>
-          <t>VARCHAR(200)</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr"/>
       <c r="D377" s="2" t="inlineStr"/>
       <c r="E377" s="2" t="inlineStr"/>
-      <c r="F377" s="5" t="inlineStr">
-        <is>
-          <t>Renamed</t>
+      <c r="F377" s="7" t="inlineStr">
+        <is>
+          <t>Removed</t>
         </is>
       </c>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>Was SSO</t>
+          <t>Duplicate of Employee_Master.Email</t>
         </is>
       </c>
     </row>
@@ -12248,20 +12225,24 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="C378" s="2" t="inlineStr"/>
+          <t>Created_By</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
       <c r="D378" s="2" t="inlineStr"/>
       <c r="E378" s="2" t="inlineStr"/>
-      <c r="F378" s="7" t="inlineStr">
-        <is>
-          <t>Removed</t>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>Kept</t>
         </is>
       </c>
       <c r="G378" s="2" t="inlineStr">
         <is>
-          <t>Duplicate of Employee_Master.Email</t>
+          <t>Audit column</t>
         </is>
       </c>
     </row>
@@ -12273,12 +12254,12 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>Created_By</t>
+          <t>Created_Date</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>DATETIME2</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr"/>
@@ -12302,12 +12283,12 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>Created_Date</t>
+          <t>Modified_By</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr"/>
@@ -12331,12 +12312,12 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>Modified_By</t>
+          <t>Modified_Date</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>DATETIME2</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr"/>
@@ -12355,29 +12336,33 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Login</t>
+          <t>ClearOps_UserLogin</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>Modified_Date</t>
+          <t>User_Login_Id</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
-        </is>
-      </c>
-      <c r="D382" s="2" t="inlineStr"/>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E382" s="2" t="inlineStr"/>
-      <c r="F382" s="2" t="inlineStr">
-        <is>
-          <t>Kept</t>
+      <c r="F382" s="6" t="inlineStr">
+        <is>
+          <t>Added</t>
         </is>
       </c>
       <c r="G382" s="2" t="inlineStr">
         <is>
-          <t>Audit column</t>
+          <t>MISSING: no PK</t>
         </is>
       </c>
     </row>
@@ -12389,7 +12374,7 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>User_Login_Id</t>
+          <t>User_Id</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
@@ -12399,18 +12384,22 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E383" s="2" t="inlineStr"/>
-      <c r="F383" s="6" t="inlineStr">
-        <is>
-          <t>Added</t>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>ClearOps_Users.User_Id</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>Kept</t>
         </is>
       </c>
       <c r="G383" s="2" t="inlineStr">
         <is>
-          <t>MISSING: no PK</t>
+          <t>Was userid</t>
         </is>
       </c>
     </row>
@@ -12422,32 +12411,24 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>User_Id</t>
+          <t>Login_DateTime</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D384" s="2" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E384" s="2" t="inlineStr">
-        <is>
-          <t>ClearOps_Users.User_Id</t>
-        </is>
-      </c>
-      <c r="F384" s="2" t="inlineStr">
-        <is>
-          <t>Kept</t>
+          <t>DATETIME2</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr"/>
+      <c r="E384" s="2" t="inlineStr"/>
+      <c r="F384" s="5" t="inlineStr">
+        <is>
+          <t>Renamed</t>
         </is>
       </c>
       <c r="G384" s="2" t="inlineStr">
         <is>
-          <t>Was userid</t>
+          <t>Was logindatetimestampe (typo)</t>
         </is>
       </c>
     </row>
@@ -12459,26 +12440,22 @@
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>Login_DateTime</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>DATETIME2</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr"/>
       <c r="E385" s="2" t="inlineStr"/>
-      <c r="F385" s="5" t="inlineStr">
-        <is>
-          <t>Renamed</t>
-        </is>
-      </c>
-      <c r="G385" s="2" t="inlineStr">
-        <is>
-          <t>Was logindatetimestampe (typo)</t>
-        </is>
-      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>Kept</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -12488,32 +12465,32 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="C386" s="2" t="inlineStr">
-        <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr"/>
       <c r="D386" s="2" t="inlineStr"/>
       <c r="E386" s="2" t="inlineStr"/>
-      <c r="F386" s="2" t="inlineStr">
-        <is>
-          <t>Kept</t>
-        </is>
-      </c>
-      <c r="G386" s="2" t="inlineStr"/>
+      <c r="F386" s="7" t="inlineStr">
+        <is>
+          <t>Removed</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate of Employee_Master.Email</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_UserLogin</t>
+          <t>RolesandPermissions</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>RoleName,RoleType,Module,Page_Id,Role_Access,AssignedUserCount,Status</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr"/>
@@ -12521,42 +12498,17 @@
       <c r="E387" s="2" t="inlineStr"/>
       <c r="F387" s="7" t="inlineStr">
         <is>
-          <t>Removed</t>
+          <t>Moved/Removed</t>
         </is>
       </c>
       <c r="G387" s="2" t="inlineStr">
         <is>
-          <t>Duplicate of Employee_Master.Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" s="2" t="inlineStr">
-        <is>
-          <t>RolesandPermissions</t>
-        </is>
-      </c>
-      <c r="B388" s="2" t="inlineStr">
-        <is>
-          <t>RoleName,RoleType,Module,Page_Id,Role_Access,AssignedUserCount,Status</t>
-        </is>
-      </c>
-      <c r="C388" s="2" t="inlineStr"/>
-      <c r="D388" s="2" t="inlineStr"/>
-      <c r="E388" s="2" t="inlineStr"/>
-      <c r="F388" s="7" t="inlineStr">
-        <is>
-          <t>Moved/Removed</t>
-        </is>
-      </c>
-      <c r="G388" s="2" t="inlineStr">
-        <is>
           <t>Fully derivable from Role, Page, Permission, Access, Users (AssignedUserCount = COUNT)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G388"/>
+  <autoFilter ref="A1:G387"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14350,7 +14302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -15594,22 +15546,22 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>ProjectManualCreation</t>
+          <t>Admin_IntegrationStatus</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>All columns</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>Moved/Removed</t>
+          <t>System_Name</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Renamed</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Duplicate of Project_Master</t>
+          <t>Was System</t>
         </is>
       </c>
     </row>
@@ -15621,7 +15573,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>System_Name</t>
+          <t>Records_Captured</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -15631,19 +15583,19 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Was System</t>
+          <t>Was record_captured</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Admin_IntegrationStatus</t>
+          <t>ClearOps_Logs</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Records_Captured</t>
+          <t>Cron_Job_Run_Id</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -15653,7 +15605,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Was record_captured</t>
+          <t>Was cornjob run_id (typo)</t>
         </is>
       </c>
     </row>
@@ -15665,17 +15617,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Cron_Job_Run_Id</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>Renamed</t>
+          <t>Run_Start</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Added</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Was cornjob run_id (typo)</t>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -15687,7 +15639,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Run_Start</t>
+          <t>Run_End</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -15709,7 +15661,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Run_End</t>
+          <t>Run_Status</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -15731,7 +15683,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Run_Status</t>
+          <t>Records_Processed</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -15753,7 +15705,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Records_Processed</t>
+          <t>Error_Message</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -15775,7 +15727,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Error_Message</t>
+          <t>Created_By</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -15785,7 +15737,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Audit column (MISSING in sheet)</t>
         </is>
       </c>
     </row>
@@ -15797,7 +15749,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Created_By</t>
+          <t>Created_Date</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -15819,7 +15771,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Created_Date</t>
+          <t>Modified_By</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -15841,7 +15793,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Modified_By</t>
+          <t>Modified_Date</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
@@ -15858,12 +15810,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Logs</t>
+          <t>ClearOps_Role</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Modified_Date</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -15873,19 +15825,19 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Audit column (MISSING in sheet)</t>
+          <t>From RolesandPermissions</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Role</t>
+          <t>ClearOps_Page</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -15895,73 +15847,73 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>From RolesandPermissions</t>
+          <t>Moved from RolesandPermissions</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Page</t>
+          <t>ClearOps_Access</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>Added</t>
+          <t>Access_Type</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Renamed</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Moved from RolesandPermissions</t>
+          <t>Was Accrss_type (typo)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Access</t>
+          <t>ClearOps_Permission</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Access_Type</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>Renamed</t>
+          <t>HRID</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>Removed</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Was Accrss_type (typo)</t>
+          <t>A role permission is not per person; user-&gt;role is in ClearOps_Users</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Permission</t>
+          <t>ClearOps_Users</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>HRID</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>Removed</t>
+          <t>User_Id</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Renamed</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>A role permission is not per person; user-&gt;role is in ClearOps_Users</t>
+          <t>Was User_ID(PK) (sr_id)</t>
         </is>
       </c>
     </row>
@@ -15973,39 +15925,39 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>User_Id</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>Renamed</t>
+          <t>Role_Name, Name, Email</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>Removed</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Was User_ID(PK) (sr_id)</t>
+          <t>Derivable via Role_Id / HRID</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Users</t>
+          <t>ClearOps_Login</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Role_Name, Name, Email</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>Removed</t>
+          <t>Login_Id</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Added</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Derivable via Role_Id / HRID</t>
+          <t>MISSING: table had no PK</t>
         </is>
       </c>
     </row>
@@ -16017,17 +15969,17 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Login_Id</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>Added</t>
+          <t>SSO_Id</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Renamed</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>MISSING: table had no PK</t>
+          <t>Was SSO</t>
         </is>
       </c>
     </row>
@@ -16039,39 +15991,39 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SSO_Id</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>Renamed</t>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Removed</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Was SSO</t>
+          <t>Duplicate of Employee_Master.Email</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_Login</t>
+          <t>ClearOps_UserLogin</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>Removed</t>
+          <t>User_Login_Id</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Added</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Duplicate of Employee_Master.Email</t>
+          <t>MISSING: no PK</t>
         </is>
       </c>
     </row>
@@ -16083,17 +16035,17 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>User_Login_Id</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>Added</t>
+          <t>Login_DateTime</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Renamed</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>MISSING: no PK</t>
+          <t>Was logindatetimestampe (typo)</t>
         </is>
       </c>
     </row>
@@ -16105,66 +16057,44 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Login_DateTime</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>Renamed</t>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>Removed</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Was logindatetimestampe (typo)</t>
+          <t>Duplicate of Employee_Master.Email</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>ClearOps_UserLogin</t>
+          <t>RolesandPermissions</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>RoleName,RoleType,Module,Page_Id,Role_Access,AssignedUserCount,Status</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Removed</t>
+          <t>Moved/Removed</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Duplicate of Employee_Master.Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>RolesandPermissions</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>RoleName,RoleType,Module,Page_Id,Role_Access,AssignedUserCount,Status</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>Moved/Removed</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
           <t>Fully derivable from Role, Page, Permission, Access, Users (AssignedUserCount = COUNT)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D82"/>
+  <autoFilter ref="A1:D81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ClearOps_Database_Mapped.xlsx
+++ b/ClearOps_Database_Mapped.xlsx
@@ -869,7 +869,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Customers as ClearOps_Customer</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
@@ -886,7 +886,7 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
@@ -896,14 +896,14 @@
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>Countries, Job Grades, Lines of Business</t>
+          <t>Countries as ClearOps_Country, Job Grades as Grades, Lines of Business as LOB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
@@ -913,14 +913,14 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Job Grades, Lines of Business, People (HR master list)</t>
+          <t>Job Grades as Grades, Lines of Business as LOB, People (HR master list) as Employee_Master</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -930,14 +930,14 @@
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>Team Members as ClearOps_TeamMember</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -947,14 +947,14 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people), Teams</t>
+          <t>Resources (bookable people) as Resources, Teams as ClearOps_Teams</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Time Off</t>
+          <t>Time Off as ClearOps_TimeOff</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -964,14 +964,14 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Holidays as ClearOps_Holiday</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Countries</t>
+          <t>Countries as ClearOps_Country</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Lines of Business</t>
+          <t>Lines of Business as LOB</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Countries</t>
+          <t>Countries as ClearOps_Country</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
@@ -1108,7 +1108,7 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
@@ -1118,14 +1118,14 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Countries, Currencies, Customers, Job Grades</t>
+          <t>Countries as ClearOps_Country, Currencies as ClearOps_Currency, Customers as ClearOps_Customer, Job Grades as Grades</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
@@ -1178,14 +1178,14 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Currencies, Customers, Lines of Business, People (HR master list)</t>
+          <t>Currencies as ClearOps_Currency, Customers as ClearOps_Customer, Lines of Business as LOB, People (HR master list) as Employee_Master</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
@@ -1195,14 +1195,14 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS), Projects</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS, Projects as Project_Master</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
@@ -1212,14 +1212,14 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Job Grades, Project Tasks (WBS), Projects</t>
+          <t>Job Grades as Grades, Project Tasks (WBS) as ClearOps_ProjectWBS, Projects as Project_Master</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
@@ -1229,14 +1229,14 @@
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
@@ -1246,14 +1246,14 @@
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Currencies, Project Tasks (WBS), Projects</t>
+          <t>Currencies as ClearOps_Currency, Project Tasks (WBS) as ClearOps_ProjectWBS, Projects as Project_Master</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS), Projects, Resources (bookable people)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS, Projects as Project_Master, Resources (bookable people) as Resources</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
@@ -1306,14 +1306,14 @@
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS), Projects, Rate Card, Resources (bookable people)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS, Projects as Project_Master, Rate Card as ClearOps_RateCard, Resources (bookable people) as Resources</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>Monthly Hours (grid cells)</t>
+          <t>Monthly Hours (grid cells) as ClearOps_ProjectSTP_Month</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Roles as ClearOps_Role</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
@@ -1373,7 +1373,7 @@
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t>Pages as ClearOps_Page</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
@@ -1390,7 +1390,7 @@
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>Access Levels</t>
+          <t>Access Levels as ClearOps_Access</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
@@ -1407,7 +1407,7 @@
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Permissions as ClearOps_Permission</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
@@ -1417,14 +1417,14 @@
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>Access Levels, Pages, Roles</t>
+          <t>Access Levels as ClearOps_Access, Pages as ClearOps_Page, Roles as ClearOps_Role</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t>Application Users</t>
+          <t>Application Users as ClearOps_Users</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
@@ -1434,14 +1434,14 @@
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list), Roles</t>
+          <t>People (HR master list) as Employee_Master, Roles as ClearOps_Role</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>Single Sign-On Link</t>
+          <t>Single Sign-On Link as ClearOps_Login</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
@@ -1451,14 +1451,14 @@
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>Login History</t>
+          <t>Login History as ClearOps_UserLogin</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Application Users</t>
+          <t>Application Users as ClearOps_Users</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
     <row r="52">
       <c r="A52" s="15" t="inlineStr">
         <is>
-          <t>Integration Status</t>
+          <t>Integration Status as Admin_IntegrationStatus</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
@@ -1518,7 +1518,7 @@
     <row r="53">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
-          <t>Integration Status</t>
+          <t>Integration Status as Admin_IntegrationStatus</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
         <is>
-          <t>Project Forecasting (OLD)</t>
+          <t>Project Forecasting (OLD) as ClearOps_ProjectForecasting</t>
         </is>
       </c>
       <c r="B57" s="14" t="inlineStr">
@@ -1578,7 +1578,7 @@
     <row r="58">
       <c r="A58" s="17" t="inlineStr">
         <is>
-          <t>Roles &amp; Permissions (OLD sheet)</t>
+          <t>Roles &amp; Permissions (OLD sheet) as RolesandPermissions</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>Lines of Business</t>
+          <t>Lines of Business as LOB</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Countries</t>
+          <t>Countries as ClearOps_Country</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Customers as ClearOps_Customer</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Holidays as ClearOps_Holiday</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>Team Members as ClearOps_TeamMember</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Time Off</t>
+          <t>Time Off as ClearOps_TimeOff</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>Monthly Hours (grid cells)</t>
+          <t>Monthly Hours (grid cells) as ClearOps_ProjectSTP_Month</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Project Forecasting (OLD)</t>
+          <t>Project Forecasting (OLD) as ClearOps_ProjectForecasting</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>Integration Status</t>
+          <t>Integration Status as Admin_IntegrationStatus</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Roles as ClearOps_Role</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t>Pages as ClearOps_Page</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Access Levels</t>
+          <t>Access Levels as ClearOps_Access</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Permissions as ClearOps_Permission</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>Application Users</t>
+          <t>Application Users as ClearOps_Users</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link</t>
+          <t>Single Sign-On Link as ClearOps_Login</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Login History</t>
+          <t>Login History as ClearOps_UserLogin</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Roles &amp; Permissions (OLD sheet)</t>
+          <t>Roles &amp; Permissions (OLD sheet) as RolesandPermissions</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
@@ -2872,7 +2872,7 @@
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B4" s="14" t="inlineStr">
@@ -2905,7 +2905,7 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
@@ -2934,7 +2934,7 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
@@ -2963,7 +2963,7 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
@@ -3021,7 +3021,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -3050,7 +3050,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3108,7 +3108,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -3138,14 +3138,14 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
@@ -3175,14 +3175,14 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>Lines of Business</t>
+          <t>Lines of Business as LOB</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3212,14 +3212,14 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>Countries</t>
+          <t>Countries as ClearOps_Country</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -3248,7 +3248,7 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -3277,7 +3277,7 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -3306,7 +3306,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -3335,7 +3335,7 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
@@ -3364,7 +3364,7 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -3393,7 +3393,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
@@ -3451,7 +3451,7 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
@@ -3480,7 +3480,7 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
@@ -3509,7 +3509,7 @@
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
@@ -3538,7 +3538,7 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
@@ -3567,7 +3567,7 @@
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
@@ -3596,7 +3596,7 @@
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
@@ -3654,7 +3654,7 @@
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
@@ -3683,7 +3683,7 @@
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
@@ -3712,7 +3712,7 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
@@ -3741,7 +3741,7 @@
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
@@ -3770,7 +3770,7 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
@@ -3799,7 +3799,7 @@
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>Lines of Business</t>
+          <t>Lines of Business as LOB</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
@@ -3832,7 +3832,7 @@
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>Lines of Business</t>
+          <t>Lines of Business as LOB</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
@@ -3861,7 +3861,7 @@
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>Lines of Business</t>
+          <t>Lines of Business as LOB</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
@@ -3890,7 +3890,7 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Lines of Business</t>
+          <t>Lines of Business as LOB</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
@@ -3919,7 +3919,7 @@
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>Lines of Business</t>
+          <t>Lines of Business as LOB</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
@@ -3948,7 +3948,7 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Lines of Business</t>
+          <t>Lines of Business as LOB</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
@@ -3977,7 +3977,7 @@
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Lines of Business</t>
+          <t>Lines of Business as LOB</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>Lines of Business</t>
+          <t>Lines of Business as LOB</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
@@ -4035,7 +4035,7 @@
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>Lines of Business</t>
+          <t>Lines of Business as LOB</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
@@ -4064,7 +4064,7 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>Lines of Business</t>
+          <t>Lines of Business as LOB</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
@@ -4093,7 +4093,7 @@
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
@@ -4126,7 +4126,7 @@
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
@@ -4155,7 +4155,7 @@
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
@@ -4184,7 +4184,7 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
@@ -4213,7 +4213,7 @@
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
@@ -4242,7 +4242,7 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="B50" s="16" t="inlineStr">
@@ -4271,7 +4271,7 @@
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="B51" s="16" t="inlineStr">
@@ -4300,7 +4300,7 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="B52" s="16" t="inlineStr">
@@ -4329,7 +4329,7 @@
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="B53" s="16" t="inlineStr">
@@ -4358,7 +4358,7 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>Countries</t>
+          <t>Countries as ClearOps_Country</t>
         </is>
       </c>
       <c r="B54" s="16" t="inlineStr">
@@ -4391,7 +4391,7 @@
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>Countries</t>
+          <t>Countries as ClearOps_Country</t>
         </is>
       </c>
       <c r="B55" s="16" t="inlineStr">
@@ -4420,7 +4420,7 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>Countries</t>
+          <t>Countries as ClearOps_Country</t>
         </is>
       </c>
       <c r="B56" s="16" t="inlineStr">
@@ -4449,7 +4449,7 @@
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>Countries</t>
+          <t>Countries as ClearOps_Country</t>
         </is>
       </c>
       <c r="B57" s="16" t="inlineStr">
@@ -4478,7 +4478,7 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>Countries</t>
+          <t>Countries as ClearOps_Country</t>
         </is>
       </c>
       <c r="B58" s="16" t="inlineStr">
@@ -4507,7 +4507,7 @@
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>Countries</t>
+          <t>Countries as ClearOps_Country</t>
         </is>
       </c>
       <c r="B59" s="16" t="inlineStr">
@@ -4536,7 +4536,7 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>Countries</t>
+          <t>Countries as ClearOps_Country</t>
         </is>
       </c>
       <c r="B60" s="16" t="inlineStr">
@@ -4565,7 +4565,7 @@
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>Countries</t>
+          <t>Countries as ClearOps_Country</t>
         </is>
       </c>
       <c r="B61" s="16" t="inlineStr">
@@ -4594,7 +4594,7 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
       <c r="B62" s="16" t="inlineStr">
@@ -4627,7 +4627,7 @@
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
       <c r="B63" s="16" t="inlineStr">
@@ -4656,7 +4656,7 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
       <c r="B64" s="16" t="inlineStr">
@@ -4685,7 +4685,7 @@
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
       <c r="B65" s="16" t="inlineStr">
@@ -4714,7 +4714,7 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
       <c r="B66" s="16" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
       <c r="B67" s="16" t="inlineStr">
@@ -4772,7 +4772,7 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
       <c r="B68" s="16" t="inlineStr">
@@ -4801,7 +4801,7 @@
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Customers as ClearOps_Customer</t>
         </is>
       </c>
       <c r="B69" s="16" t="inlineStr">
@@ -4834,7 +4834,7 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Customers as ClearOps_Customer</t>
         </is>
       </c>
       <c r="B70" s="16" t="inlineStr">
@@ -4863,7 +4863,7 @@
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Customers as ClearOps_Customer</t>
         </is>
       </c>
       <c r="B71" s="16" t="inlineStr">
@@ -4892,7 +4892,7 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Customers as ClearOps_Customer</t>
         </is>
       </c>
       <c r="B72" s="16" t="inlineStr">
@@ -4921,7 +4921,7 @@
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Customers as ClearOps_Customer</t>
         </is>
       </c>
       <c r="B73" s="16" t="inlineStr">
@@ -4950,7 +4950,7 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Customers as ClearOps_Customer</t>
         </is>
       </c>
       <c r="B74" s="16" t="inlineStr">
@@ -4979,7 +4979,7 @@
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Customers as ClearOps_Customer</t>
         </is>
       </c>
       <c r="B75" s="16" t="inlineStr">
@@ -5008,7 +5008,7 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Customers as ClearOps_Customer</t>
         </is>
       </c>
       <c r="B76" s="16" t="inlineStr">
@@ -5037,7 +5037,7 @@
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Customers as ClearOps_Customer</t>
         </is>
       </c>
       <c r="B77" s="16" t="inlineStr">
@@ -5066,7 +5066,7 @@
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Unique number of each row in Exchange Rates</t>
+          <t>Unique number of each row in Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="79">
       <c r="A79" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B79" s="15" t="inlineStr">
@@ -5129,14 +5129,14 @@
       </c>
       <c r="G79" s="14" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
@@ -5166,14 +5166,14 @@
       </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
@@ -5202,7 +5202,7 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B82" s="16" t="inlineStr">
@@ -5231,7 +5231,7 @@
     <row r="83">
       <c r="A83" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B83" s="16" t="inlineStr">
@@ -5260,7 +5260,7 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
@@ -5289,7 +5289,7 @@
     <row r="85">
       <c r="A85" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
@@ -5318,7 +5318,7 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
@@ -5347,7 +5347,7 @@
     <row r="87">
       <c r="A87" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B87" s="14" t="inlineStr">
@@ -5376,7 +5376,7 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
@@ -5405,7 +5405,7 @@
     <row r="89">
       <c r="A89" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B89" s="14" t="inlineStr">
@@ -5434,7 +5434,7 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
@@ -5463,7 +5463,7 @@
     <row r="91">
       <c r="A91" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B91" s="14" t="inlineStr">
@@ -5492,7 +5492,7 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
@@ -5521,7 +5521,7 @@
     <row r="93">
       <c r="A93" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="B93" s="14" t="inlineStr">
@@ -5554,7 +5554,7 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
@@ -5584,14 +5584,14 @@
       </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Customers as ClearOps_Customer</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="B95" s="14" t="inlineStr">
@@ -5621,14 +5621,14 @@
       </c>
       <c r="G95" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
@@ -5657,7 +5657,7 @@
     <row r="97">
       <c r="A97" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="B97" s="14" t="inlineStr">
@@ -5686,7 +5686,7 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
@@ -5715,7 +5715,7 @@
     <row r="99">
       <c r="A99" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="B99" s="14" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
@@ -5773,7 +5773,7 @@
     <row r="101">
       <c r="A101" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="B101" s="15" t="inlineStr">
@@ -5803,14 +5803,14 @@
       </c>
       <c r="G101" s="14" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -5840,14 +5840,14 @@
       </c>
       <c r="G102" s="14" t="inlineStr">
         <is>
-          <t>Countries</t>
+          <t>Countries as ClearOps_Country</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="B103" s="14" t="inlineStr">
@@ -5876,7 +5876,7 @@
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
@@ -5905,7 +5905,7 @@
     <row r="105">
       <c r="A105" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="B105" s="14" t="inlineStr">
@@ -5934,7 +5934,7 @@
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
@@ -5963,7 +5963,7 @@
     <row r="107">
       <c r="A107" s="14" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Holidays as ClearOps_Holiday</t>
         </is>
       </c>
       <c r="B107" s="14" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>Unique number of each row in Holidays</t>
+          <t>Unique number of each row in Holidays as ClearOps_Holiday</t>
         </is>
       </c>
       <c r="F107" s="14" t="inlineStr">
@@ -5996,7 +5996,7 @@
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Holidays as ClearOps_Holiday</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
@@ -6026,14 +6026,14 @@
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>Countries</t>
+          <t>Countries as ClearOps_Country</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="14" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Holidays as ClearOps_Holiday</t>
         </is>
       </c>
       <c r="B109" s="14" t="inlineStr">
@@ -6062,7 +6062,7 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Holidays as ClearOps_Holiday</t>
         </is>
       </c>
       <c r="B110" s="16" t="inlineStr">
@@ -6091,7 +6091,7 @@
     <row r="111">
       <c r="A111" s="14" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Holidays as ClearOps_Holiday</t>
         </is>
       </c>
       <c r="B111" s="14" t="inlineStr">
@@ -6120,7 +6120,7 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Holidays as ClearOps_Holiday</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
@@ -6149,7 +6149,7 @@
     <row r="113">
       <c r="A113" s="14" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Holidays as ClearOps_Holiday</t>
         </is>
       </c>
       <c r="B113" s="14" t="inlineStr">
@@ -6178,7 +6178,7 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Holidays as ClearOps_Holiday</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
@@ -6207,7 +6207,7 @@
     <row r="115">
       <c r="A115" s="14" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Holidays as ClearOps_Holiday</t>
         </is>
       </c>
       <c r="B115" s="14" t="inlineStr">
@@ -6236,7 +6236,7 @@
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>Unique number of each row in Pass-through Costs [Was Pass_Thorugh_Id (typo)]</t>
+          <t>Unique number of each row in Pass-through Costs as ClearOps_Passthrough [Was Pass_Thorugh_Id (typo)]</t>
         </is>
       </c>
       <c r="F116" s="14" t="inlineStr">
@@ -6269,7 +6269,7 @@
     <row r="117">
       <c r="A117" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="B117" s="14" t="inlineStr">
@@ -6299,14 +6299,14 @@
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="B118" s="16" t="inlineStr">
@@ -6336,14 +6336,14 @@
       </c>
       <c r="G118" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="B119" s="14" t="inlineStr">
@@ -6372,7 +6372,7 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
@@ -6401,7 +6401,7 @@
     <row r="121">
       <c r="A121" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="B121" s="14" t="inlineStr">
@@ -6430,7 +6430,7 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
@@ -6459,7 +6459,7 @@
     <row r="123">
       <c r="A123" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="B123" s="14" t="inlineStr">
@@ -6488,7 +6488,7 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
@@ -6517,7 +6517,7 @@
     <row r="125">
       <c r="A125" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="B125" s="15" t="inlineStr">
@@ -6547,14 +6547,14 @@
       </c>
       <c r="G125" s="14" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
@@ -6583,7 +6583,7 @@
     <row r="127">
       <c r="A127" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="B127" s="14" t="inlineStr">
@@ -6612,7 +6612,7 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
@@ -6641,7 +6641,7 @@
     <row r="129">
       <c r="A129" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="B129" s="14" t="inlineStr">
@@ -6670,7 +6670,7 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
@@ -6703,7 +6703,7 @@
     <row r="131">
       <c r="A131" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="B131" s="14" t="inlineStr">
@@ -6733,14 +6733,14 @@
       </c>
       <c r="G131" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
@@ -6769,7 +6769,7 @@
     <row r="133">
       <c r="A133" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="B133" s="14" t="inlineStr">
@@ -6798,7 +6798,7 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
@@ -6827,7 +6827,7 @@
     <row r="135">
       <c r="A135" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="B135" s="14" t="inlineStr">
@@ -6856,7 +6856,7 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
@@ -6886,14 +6886,14 @@
       </c>
       <c r="G136" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="B137" s="14" t="inlineStr">
@@ -6923,14 +6923,14 @@
       </c>
       <c r="G137" s="14" t="inlineStr">
         <is>
-          <t>Lines of Business</t>
+          <t>Lines of Business as LOB</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
@@ -6959,7 +6959,7 @@
     <row r="139">
       <c r="A139" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="B139" s="14" t="inlineStr">
@@ -6988,7 +6988,7 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
@@ -7017,7 +7017,7 @@
     <row r="141">
       <c r="A141" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="B141" s="14" t="inlineStr">
@@ -7046,7 +7046,7 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
@@ -7075,7 +7075,7 @@
     <row r="143">
       <c r="A143" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="B143" s="14" t="inlineStr">
@@ -7104,7 +7104,7 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
@@ -7133,7 +7133,7 @@
     <row r="145">
       <c r="A145" s="14" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
       <c r="B145" s="14" t="inlineStr">
@@ -7166,7 +7166,7 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
@@ -7195,7 +7195,7 @@
     <row r="147">
       <c r="A147" s="14" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
       <c r="B147" s="14" t="inlineStr">
@@ -7224,7 +7224,7 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
@@ -7254,14 +7254,14 @@
       </c>
       <c r="G148" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="14" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
       <c r="B149" s="15" t="inlineStr">
@@ -7291,14 +7291,14 @@
       </c>
       <c r="G149" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
@@ -7327,7 +7327,7 @@
     <row r="151">
       <c r="A151" s="14" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
       <c r="B151" s="14" t="inlineStr">
@@ -7356,7 +7356,7 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
@@ -7385,7 +7385,7 @@
     <row r="153">
       <c r="A153" s="14" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
       <c r="B153" s="14" t="inlineStr">
@@ -7414,7 +7414,7 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>Team Members as ClearOps_TeamMember</t>
         </is>
       </c>
       <c r="B154" s="16" t="inlineStr">
@@ -7444,14 +7444,14 @@
       </c>
       <c r="G154" s="14" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="13" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>Team Members as ClearOps_TeamMember</t>
         </is>
       </c>
       <c r="B155" s="16" t="inlineStr">
@@ -7481,14 +7481,14 @@
       </c>
       <c r="G155" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>Team Members as ClearOps_TeamMember</t>
         </is>
       </c>
       <c r="B156" s="16" t="inlineStr">
@@ -7517,7 +7517,7 @@
     <row r="157">
       <c r="A157" s="13" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>Team Members as ClearOps_TeamMember</t>
         </is>
       </c>
       <c r="B157" s="16" t="inlineStr">
@@ -7546,7 +7546,7 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>Team Members as ClearOps_TeamMember</t>
         </is>
       </c>
       <c r="B158" s="16" t="inlineStr">
@@ -7575,7 +7575,7 @@
     <row r="159">
       <c r="A159" s="13" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>Team Members as ClearOps_TeamMember</t>
         </is>
       </c>
       <c r="B159" s="16" t="inlineStr">
@@ -7604,7 +7604,7 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>Team Members as ClearOps_TeamMember</t>
         </is>
       </c>
       <c r="B160" s="16" t="inlineStr">
@@ -7633,7 +7633,7 @@
     <row r="161">
       <c r="A161" s="13" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>Team Members as ClearOps_TeamMember</t>
         </is>
       </c>
       <c r="B161" s="16" t="inlineStr">
@@ -7662,7 +7662,7 @@
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
         <is>
-          <t>Time Off</t>
+          <t>Time Off as ClearOps_TimeOff</t>
         </is>
       </c>
       <c r="B162" s="14" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>Unique number of each row in Time Off</t>
+          <t>Unique number of each row in Time Off as ClearOps_TimeOff</t>
         </is>
       </c>
       <c r="F162" s="14" t="inlineStr">
@@ -7695,7 +7695,7 @@
     <row r="163">
       <c r="A163" s="14" t="inlineStr">
         <is>
-          <t>Time Off</t>
+          <t>Time Off as ClearOps_TimeOff</t>
         </is>
       </c>
       <c r="B163" s="14" t="inlineStr">
@@ -7725,14 +7725,14 @@
       </c>
       <c r="G163" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
         <is>
-          <t>Time Off</t>
+          <t>Time Off as ClearOps_TimeOff</t>
         </is>
       </c>
       <c r="B164" s="14" t="inlineStr">
@@ -7761,7 +7761,7 @@
     <row r="165">
       <c r="A165" s="14" t="inlineStr">
         <is>
-          <t>Time Off</t>
+          <t>Time Off as ClearOps_TimeOff</t>
         </is>
       </c>
       <c r="B165" s="16" t="inlineStr">
@@ -7790,7 +7790,7 @@
     <row r="166">
       <c r="A166" s="14" t="inlineStr">
         <is>
-          <t>Time Off</t>
+          <t>Time Off as ClearOps_TimeOff</t>
         </is>
       </c>
       <c r="B166" s="16" t="inlineStr">
@@ -7819,7 +7819,7 @@
     <row r="167">
       <c r="A167" s="14" t="inlineStr">
         <is>
-          <t>Time Off</t>
+          <t>Time Off as ClearOps_TimeOff</t>
         </is>
       </c>
       <c r="B167" s="14" t="inlineStr">
@@ -7848,7 +7848,7 @@
     <row r="168">
       <c r="A168" s="14" t="inlineStr">
         <is>
-          <t>Time Off</t>
+          <t>Time Off as ClearOps_TimeOff</t>
         </is>
       </c>
       <c r="B168" s="14" t="inlineStr">
@@ -7877,7 +7877,7 @@
     <row r="169">
       <c r="A169" s="14" t="inlineStr">
         <is>
-          <t>Time Off</t>
+          <t>Time Off as ClearOps_TimeOff</t>
         </is>
       </c>
       <c r="B169" s="14" t="inlineStr">
@@ -7906,7 +7906,7 @@
     <row r="170">
       <c r="A170" s="14" t="inlineStr">
         <is>
-          <t>Time Off</t>
+          <t>Time Off as ClearOps_TimeOff</t>
         </is>
       </c>
       <c r="B170" s="14" t="inlineStr">
@@ -7935,7 +7935,7 @@
     <row r="171">
       <c r="A171" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B171" s="15" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
-          <t>Unique number of each row in Time Planner [Was Project_Time_Panner_id (typo)]</t>
+          <t>Unique number of each row in Time Planner as ClearOps_ProjectTimePlanner [Was Project_Time_Panner_id (typo)]</t>
         </is>
       </c>
       <c r="F171" s="14" t="inlineStr">
@@ -7968,7 +7968,7 @@
     <row r="172">
       <c r="A172" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B172" s="16" t="inlineStr">
@@ -7998,14 +7998,14 @@
       </c>
       <c r="G172" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B173" s="14" t="inlineStr">
@@ -8035,14 +8035,14 @@
       </c>
       <c r="G173" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B174" s="14" t="inlineStr">
@@ -8072,14 +8072,14 @@
       </c>
       <c r="G174" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B175" s="14" t="inlineStr">
@@ -8108,7 +8108,7 @@
     <row r="176">
       <c r="A176" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B176" s="14" t="inlineStr">
@@ -8137,7 +8137,7 @@
     <row r="177">
       <c r="A177" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B177" s="14" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="178">
       <c r="A178" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B178" s="14" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="179">
       <c r="A179" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B179" s="14" t="inlineStr">
@@ -8224,7 +8224,7 @@
     <row r="180">
       <c r="A180" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B180" s="14" t="inlineStr">
@@ -8253,7 +8253,7 @@
     <row r="181">
       <c r="A181" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B181" s="14" t="inlineStr">
@@ -8282,7 +8282,7 @@
     <row r="182">
       <c r="A182" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B182" s="14" t="inlineStr">
@@ -8311,7 +8311,7 @@
     <row r="183">
       <c r="A183" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B183" s="14" t="inlineStr">
@@ -8340,7 +8340,7 @@
     <row r="184">
       <c r="A184" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B184" s="14" t="inlineStr">
@@ -8369,7 +8369,7 @@
     <row r="185">
       <c r="A185" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B185" s="14" t="inlineStr">
@@ -8398,7 +8398,7 @@
     <row r="186">
       <c r="A186" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B186" s="14" t="inlineStr">
@@ -8427,7 +8427,7 @@
     <row r="187">
       <c r="A187" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B187" s="14" t="inlineStr">
@@ -8460,7 +8460,7 @@
     <row r="188">
       <c r="A188" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B188" s="14" t="inlineStr">
@@ -8489,7 +8489,7 @@
     <row r="189">
       <c r="A189" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B189" s="14" t="inlineStr">
@@ -8518,7 +8518,7 @@
     <row r="190">
       <c r="A190" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B190" s="14" t="inlineStr">
@@ -8547,7 +8547,7 @@
     <row r="191">
       <c r="A191" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B191" s="14" t="inlineStr">
@@ -8576,7 +8576,7 @@
     <row r="192">
       <c r="A192" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B192" s="15" t="inlineStr">
@@ -8606,14 +8606,14 @@
       </c>
       <c r="G192" s="14" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Customers as ClearOps_Customer</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B193" s="14" t="inlineStr">
@@ -8643,14 +8643,14 @@
       </c>
       <c r="G193" s="14" t="inlineStr">
         <is>
-          <t>Lines of Business</t>
+          <t>Lines of Business as LOB</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B194" s="14" t="inlineStr">
@@ -8679,7 +8679,7 @@
     <row r="195">
       <c r="A195" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B195" s="14" t="inlineStr">
@@ -8708,7 +8708,7 @@
     <row r="196">
       <c r="A196" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B196" s="14" t="inlineStr">
@@ -8737,7 +8737,7 @@
     <row r="197">
       <c r="A197" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B197" s="14" t="inlineStr">
@@ -8766,7 +8766,7 @@
     <row r="198">
       <c r="A198" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B198" s="15" t="inlineStr">
@@ -8796,14 +8796,14 @@
       </c>
       <c r="G198" s="14" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B199" s="15" t="inlineStr">
@@ -8833,14 +8833,14 @@
       </c>
       <c r="G199" s="14" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B200" s="14" t="inlineStr">
@@ -8869,7 +8869,7 @@
     <row r="201">
       <c r="A201" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B201" s="14" t="inlineStr">
@@ -8898,7 +8898,7 @@
     <row r="202">
       <c r="A202" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B202" s="14" t="inlineStr">
@@ -8927,7 +8927,7 @@
     <row r="203">
       <c r="A203" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B203" s="14" t="inlineStr">
@@ -8956,7 +8956,7 @@
     <row r="204">
       <c r="A204" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B204" s="14" t="inlineStr">
@@ -8985,7 +8985,7 @@
     <row r="205">
       <c r="A205" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B205" s="14" t="inlineStr">
@@ -9014,7 +9014,7 @@
     <row r="206">
       <c r="A206" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B206" s="14" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="207">
       <c r="A207" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B207" s="14" t="inlineStr">
@@ -9072,7 +9072,7 @@
     <row r="208">
       <c r="A208" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B208" s="14" t="inlineStr">
@@ -9101,7 +9101,7 @@
     <row r="209">
       <c r="A209" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B209" s="14" t="inlineStr">
@@ -9130,7 +9130,7 @@
     <row r="210">
       <c r="A210" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B210" s="14" t="inlineStr">
@@ -9159,7 +9159,7 @@
     <row r="211">
       <c r="A211" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B211" s="14" t="inlineStr">
@@ -9189,14 +9189,14 @@
       </c>
       <c r="G211" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B212" s="14" t="inlineStr">
@@ -9226,14 +9226,14 @@
       </c>
       <c r="G212" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B213" s="14" t="inlineStr">
@@ -9263,14 +9263,14 @@
       </c>
       <c r="G213" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B214" s="14" t="inlineStr">
@@ -9300,14 +9300,14 @@
       </c>
       <c r="G214" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B215" s="14" t="inlineStr">
@@ -9337,14 +9337,14 @@
       </c>
       <c r="G215" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B216" s="14" t="inlineStr">
@@ -9374,14 +9374,14 @@
       </c>
       <c r="G216" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B217" s="16" t="inlineStr">
@@ -9410,7 +9410,7 @@
     <row r="218">
       <c r="A218" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B218" s="14" t="inlineStr">
@@ -9439,7 +9439,7 @@
     <row r="219">
       <c r="A219" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B219" s="14" t="inlineStr">
@@ -9468,7 +9468,7 @@
     <row r="220">
       <c r="A220" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B220" s="14" t="inlineStr">
@@ -9497,7 +9497,7 @@
     <row r="221">
       <c r="A221" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B221" s="14" t="inlineStr">
@@ -9526,7 +9526,7 @@
     <row r="222">
       <c r="A222" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B222" s="15" t="inlineStr">
@@ -9559,7 +9559,7 @@
     <row r="223">
       <c r="A223" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B223" s="14" t="inlineStr">
@@ -9589,14 +9589,14 @@
       </c>
       <c r="G223" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B224" s="15" t="inlineStr">
@@ -9626,14 +9626,14 @@
       </c>
       <c r="G224" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B225" s="14" t="inlineStr">
@@ -9663,14 +9663,14 @@
       </c>
       <c r="G225" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B226" s="14" t="inlineStr">
@@ -9699,7 +9699,7 @@
     <row r="227">
       <c r="A227" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B227" s="16" t="inlineStr">
@@ -9728,7 +9728,7 @@
     <row r="228">
       <c r="A228" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B228" s="15" t="inlineStr">
@@ -9757,7 +9757,7 @@
     <row r="229">
       <c r="A229" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B229" s="14" t="inlineStr">
@@ -9786,7 +9786,7 @@
     <row r="230">
       <c r="A230" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B230" s="14" t="inlineStr">
@@ -9815,7 +9815,7 @@
     <row r="231">
       <c r="A231" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B231" s="14" t="inlineStr">
@@ -9844,7 +9844,7 @@
     <row r="232">
       <c r="A232" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B232" s="14" t="inlineStr">
@@ -9873,7 +9873,7 @@
     <row r="233">
       <c r="A233" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B233" s="14" t="inlineStr">
@@ -9902,7 +9902,7 @@
     <row r="234">
       <c r="A234" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B234" s="14" t="inlineStr">
@@ -9931,7 +9931,7 @@
     <row r="235">
       <c r="A235" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B235" s="14" t="inlineStr">
@@ -9960,7 +9960,7 @@
     <row r="236">
       <c r="A236" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B236" s="15" t="inlineStr">
@@ -9989,7 +9989,7 @@
     <row r="237">
       <c r="A237" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B237" s="15" t="inlineStr">
@@ -10018,7 +10018,7 @@
     <row r="238">
       <c r="A238" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B238" s="14" t="inlineStr">
@@ -10047,7 +10047,7 @@
     <row r="239">
       <c r="A239" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B239" s="14" t="inlineStr">
@@ -10076,7 +10076,7 @@
     <row r="240">
       <c r="A240" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B240" s="14" t="inlineStr">
@@ -10105,7 +10105,7 @@
     <row r="241">
       <c r="A241" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B241" s="14" t="inlineStr">
@@ -10134,7 +10134,7 @@
     <row r="242">
       <c r="A242" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B242" s="14" t="inlineStr">
@@ -10163,7 +10163,7 @@
     <row r="243">
       <c r="A243" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B243" s="14" t="inlineStr">
@@ -10192,7 +10192,7 @@
     <row r="244">
       <c r="A244" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B244" s="14" t="inlineStr">
@@ -10221,7 +10221,7 @@
     <row r="245">
       <c r="A245" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B245" s="14" t="inlineStr">
@@ -10250,7 +10250,7 @@
     <row r="246">
       <c r="A246" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B246" s="14" t="inlineStr">
@@ -10279,7 +10279,7 @@
     <row r="247">
       <c r="A247" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="B247" s="15" t="inlineStr">
@@ -10312,7 +10312,7 @@
     <row r="248">
       <c r="A248" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="B248" s="14" t="inlineStr">
@@ -10342,14 +10342,14 @@
       </c>
       <c r="G248" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="B249" s="14" t="inlineStr">
@@ -10379,14 +10379,14 @@
       </c>
       <c r="G249" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="B250" s="15" t="inlineStr">
@@ -10416,14 +10416,14 @@
       </c>
       <c r="G250" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="B251" s="14" t="inlineStr">
@@ -10452,7 +10452,7 @@
     <row r="252">
       <c r="A252" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="B252" s="14" t="inlineStr">
@@ -10481,7 +10481,7 @@
     <row r="253">
       <c r="A253" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="B253" s="14" t="inlineStr">
@@ -10510,7 +10510,7 @@
     <row r="254">
       <c r="A254" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="B254" s="14" t="inlineStr">
@@ -10539,7 +10539,7 @@
     <row r="255">
       <c r="A255" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="B255" s="14" t="inlineStr">
@@ -10568,7 +10568,7 @@
     <row r="256">
       <c r="A256" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="B256" s="14" t="inlineStr">
@@ -10597,7 +10597,7 @@
     <row r="257">
       <c r="A257" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="B257" s="14" t="inlineStr">
@@ -10626,7 +10626,7 @@
     <row r="258">
       <c r="A258" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="B258" s="14" t="inlineStr">
@@ -10655,7 +10655,7 @@
     <row r="259">
       <c r="A259" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="B259" s="14" t="inlineStr">
@@ -10684,7 +10684,7 @@
     <row r="260">
       <c r="A260" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="B260" s="14" t="inlineStr">
@@ -10713,7 +10713,7 @@
     <row r="261">
       <c r="A261" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="B261" s="14" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="E261" s="14" t="inlineStr">
         <is>
-          <t>Unique number of each row in Project Finance Settings</t>
+          <t>Unique number of each row in Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="F261" s="14" t="inlineStr">
@@ -10746,7 +10746,7 @@
     <row r="262">
       <c r="A262" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="B262" s="14" t="inlineStr">
@@ -10776,14 +10776,14 @@
       </c>
       <c r="G262" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="B263" s="14" t="inlineStr">
@@ -10812,7 +10812,7 @@
     <row r="264">
       <c r="A264" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="B264" s="14" t="inlineStr">
@@ -10841,7 +10841,7 @@
     <row r="265">
       <c r="A265" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="B265" s="14" t="inlineStr">
@@ -10870,7 +10870,7 @@
     <row r="266">
       <c r="A266" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="B266" s="14" t="inlineStr">
@@ -10899,7 +10899,7 @@
     <row r="267">
       <c r="A267" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="B267" s="14" t="inlineStr">
@@ -10928,7 +10928,7 @@
     <row r="268">
       <c r="A268" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="B268" s="14" t="inlineStr">
@@ -10957,7 +10957,7 @@
     <row r="269">
       <c r="A269" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="B269" s="14" t="inlineStr">
@@ -10986,7 +10986,7 @@
     <row r="270">
       <c r="A270" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="B270" s="14" t="inlineStr">
@@ -11015,7 +11015,7 @@
     <row r="271">
       <c r="A271" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="B271" s="14" t="inlineStr">
@@ -11044,7 +11044,7 @@
     <row r="272">
       <c r="A272" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="B272" s="14" t="inlineStr">
@@ -11073,7 +11073,7 @@
     <row r="273">
       <c r="A273" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="B273" s="14" t="inlineStr">
@@ -11102,7 +11102,7 @@
     <row r="274">
       <c r="A274" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="B274" s="14" t="inlineStr">
@@ -11131,7 +11131,7 @@
     <row r="275">
       <c r="A275" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B275" s="14" t="inlineStr">
@@ -11164,7 +11164,7 @@
     <row r="276">
       <c r="A276" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B276" s="14" t="inlineStr">
@@ -11194,14 +11194,14 @@
       </c>
       <c r="G276" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B277" s="14" t="inlineStr">
@@ -11231,14 +11231,14 @@
       </c>
       <c r="G277" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B278" s="15" t="inlineStr">
@@ -11268,14 +11268,14 @@
       </c>
       <c r="G278" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B279" s="15" t="inlineStr">
@@ -11305,14 +11305,14 @@
       </c>
       <c r="G279" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B280" s="16" t="inlineStr">
@@ -11341,7 +11341,7 @@
     <row r="281">
       <c r="A281" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B281" s="16" t="inlineStr">
@@ -11370,7 +11370,7 @@
     <row r="282">
       <c r="A282" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B282" s="14" t="inlineStr">
@@ -11399,7 +11399,7 @@
     <row r="283">
       <c r="A283" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B283" s="14" t="inlineStr">
@@ -11428,7 +11428,7 @@
     <row r="284">
       <c r="A284" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B284" s="14" t="inlineStr">
@@ -11457,7 +11457,7 @@
     <row r="285">
       <c r="A285" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B285" s="14" t="inlineStr">
@@ -11486,7 +11486,7 @@
     <row r="286">
       <c r="A286" s="13" t="inlineStr">
         <is>
-          <t>Monthly Hours (grid cells)</t>
+          <t>Monthly Hours (grid cells) as ClearOps_ProjectSTP_Month</t>
         </is>
       </c>
       <c r="B286" s="16" t="inlineStr">
@@ -11516,14 +11516,14 @@
       </c>
       <c r="G286" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="13" t="inlineStr">
         <is>
-          <t>Monthly Hours (grid cells)</t>
+          <t>Monthly Hours (grid cells) as ClearOps_ProjectSTP_Month</t>
         </is>
       </c>
       <c r="B287" s="16" t="inlineStr">
@@ -11556,7 +11556,7 @@
     <row r="288">
       <c r="A288" s="13" t="inlineStr">
         <is>
-          <t>Monthly Hours (grid cells)</t>
+          <t>Monthly Hours (grid cells) as ClearOps_ProjectSTP_Month</t>
         </is>
       </c>
       <c r="B288" s="16" t="inlineStr">
@@ -11585,7 +11585,7 @@
     <row r="289">
       <c r="A289" s="13" t="inlineStr">
         <is>
-          <t>Monthly Hours (grid cells)</t>
+          <t>Monthly Hours (grid cells) as ClearOps_ProjectSTP_Month</t>
         </is>
       </c>
       <c r="B289" s="16" t="inlineStr">
@@ -11614,7 +11614,7 @@
     <row r="290">
       <c r="A290" s="13" t="inlineStr">
         <is>
-          <t>Monthly Hours (grid cells)</t>
+          <t>Monthly Hours (grid cells) as ClearOps_ProjectSTP_Month</t>
         </is>
       </c>
       <c r="B290" s="16" t="inlineStr">
@@ -11643,7 +11643,7 @@
     <row r="291">
       <c r="A291" s="13" t="inlineStr">
         <is>
-          <t>Monthly Hours (grid cells)</t>
+          <t>Monthly Hours (grid cells) as ClearOps_ProjectSTP_Month</t>
         </is>
       </c>
       <c r="B291" s="16" t="inlineStr">
@@ -11672,7 +11672,7 @@
     <row r="292">
       <c r="A292" s="13" t="inlineStr">
         <is>
-          <t>Monthly Hours (grid cells)</t>
+          <t>Monthly Hours (grid cells) as ClearOps_ProjectSTP_Month</t>
         </is>
       </c>
       <c r="B292" s="16" t="inlineStr">
@@ -11701,7 +11701,7 @@
     <row r="293">
       <c r="A293" s="13" t="inlineStr">
         <is>
-          <t>Monthly Hours (grid cells)</t>
+          <t>Monthly Hours (grid cells) as ClearOps_ProjectSTP_Month</t>
         </is>
       </c>
       <c r="B293" s="16" t="inlineStr">
@@ -11730,7 +11730,7 @@
     <row r="294">
       <c r="A294" s="13" t="inlineStr">
         <is>
-          <t>Monthly Hours (grid cells)</t>
+          <t>Monthly Hours (grid cells) as ClearOps_ProjectSTP_Month</t>
         </is>
       </c>
       <c r="B294" s="16" t="inlineStr">
@@ -11759,7 +11759,7 @@
     <row r="295">
       <c r="A295" s="13" t="inlineStr">
         <is>
-          <t>Monthly Hours (grid cells)</t>
+          <t>Monthly Hours (grid cells) as ClearOps_ProjectSTP_Month</t>
         </is>
       </c>
       <c r="B295" s="16" t="inlineStr">
@@ -11788,7 +11788,7 @@
     <row r="296">
       <c r="A296" s="13" t="inlineStr">
         <is>
-          <t>Monthly Hours (grid cells)</t>
+          <t>Monthly Hours (grid cells) as ClearOps_ProjectSTP_Month</t>
         </is>
       </c>
       <c r="B296" s="16" t="inlineStr">
@@ -11817,7 +11817,7 @@
     <row r="297">
       <c r="A297" s="14" t="inlineStr">
         <is>
-          <t>Integration Status</t>
+          <t>Integration Status as Admin_IntegrationStatus</t>
         </is>
       </c>
       <c r="B297" s="14" t="inlineStr">
@@ -11850,7 +11850,7 @@
     <row r="298">
       <c r="A298" s="14" t="inlineStr">
         <is>
-          <t>Integration Status</t>
+          <t>Integration Status as Admin_IntegrationStatus</t>
         </is>
       </c>
       <c r="B298" s="15" t="inlineStr">
@@ -11879,7 +11879,7 @@
     <row r="299">
       <c r="A299" s="14" t="inlineStr">
         <is>
-          <t>Integration Status</t>
+          <t>Integration Status as Admin_IntegrationStatus</t>
         </is>
       </c>
       <c r="B299" s="14" t="inlineStr">
@@ -11908,7 +11908,7 @@
     <row r="300">
       <c r="A300" s="14" t="inlineStr">
         <is>
-          <t>Integration Status</t>
+          <t>Integration Status as Admin_IntegrationStatus</t>
         </is>
       </c>
       <c r="B300" s="14" t="inlineStr">
@@ -11937,7 +11937,7 @@
     <row r="301">
       <c r="A301" s="14" t="inlineStr">
         <is>
-          <t>Integration Status</t>
+          <t>Integration Status as Admin_IntegrationStatus</t>
         </is>
       </c>
       <c r="B301" s="15" t="inlineStr">
@@ -11966,7 +11966,7 @@
     <row r="302">
       <c r="A302" s="14" t="inlineStr">
         <is>
-          <t>Integration Status</t>
+          <t>Integration Status as Admin_IntegrationStatus</t>
         </is>
       </c>
       <c r="B302" s="14" t="inlineStr">
@@ -11995,7 +11995,7 @@
     <row r="303">
       <c r="A303" s="14" t="inlineStr">
         <is>
-          <t>Integration Status</t>
+          <t>Integration Status as Admin_IntegrationStatus</t>
         </is>
       </c>
       <c r="B303" s="14" t="inlineStr">
@@ -12024,7 +12024,7 @@
     <row r="304">
       <c r="A304" s="14" t="inlineStr">
         <is>
-          <t>Integration Status</t>
+          <t>Integration Status as Admin_IntegrationStatus</t>
         </is>
       </c>
       <c r="B304" s="14" t="inlineStr">
@@ -12053,7 +12053,7 @@
     <row r="305">
       <c r="A305" s="14" t="inlineStr">
         <is>
-          <t>Integration Status</t>
+          <t>Integration Status as Admin_IntegrationStatus</t>
         </is>
       </c>
       <c r="B305" s="14" t="inlineStr">
@@ -12082,7 +12082,7 @@
     <row r="306">
       <c r="A306" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B306" s="14" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="E306" s="14" t="inlineStr">
         <is>
-          <t>Unique number of each row in Integration Run Log</t>
+          <t>Unique number of each row in Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="F306" s="14" t="inlineStr">
@@ -12115,7 +12115,7 @@
     <row r="307">
       <c r="A307" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B307" s="14" t="inlineStr">
@@ -12145,14 +12145,14 @@
       </c>
       <c r="G307" s="14" t="inlineStr">
         <is>
-          <t>Integration Status</t>
+          <t>Integration Status as Admin_IntegrationStatus</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B308" s="15" t="inlineStr">
@@ -12181,7 +12181,7 @@
     <row r="309">
       <c r="A309" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B309" s="16" t="inlineStr">
@@ -12210,7 +12210,7 @@
     <row r="310">
       <c r="A310" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B310" s="16" t="inlineStr">
@@ -12239,7 +12239,7 @@
     <row r="311">
       <c r="A311" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B311" s="16" t="inlineStr">
@@ -12268,7 +12268,7 @@
     <row r="312">
       <c r="A312" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B312" s="16" t="inlineStr">
@@ -12297,7 +12297,7 @@
     <row r="313">
       <c r="A313" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B313" s="16" t="inlineStr">
@@ -12326,7 +12326,7 @@
     <row r="314">
       <c r="A314" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B314" s="16" t="inlineStr">
@@ -12355,7 +12355,7 @@
     <row r="315">
       <c r="A315" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B315" s="16" t="inlineStr">
@@ -12384,7 +12384,7 @@
     <row r="316">
       <c r="A316" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B316" s="16" t="inlineStr">
@@ -12413,7 +12413,7 @@
     <row r="317">
       <c r="A317" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B317" s="16" t="inlineStr">
@@ -12442,7 +12442,7 @@
     <row r="318">
       <c r="A318" s="14" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Roles as ClearOps_Role</t>
         </is>
       </c>
       <c r="B318" s="14" t="inlineStr">
@@ -12475,7 +12475,7 @@
     <row r="319">
       <c r="A319" s="14" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Roles as ClearOps_Role</t>
         </is>
       </c>
       <c r="B319" s="14" t="inlineStr">
@@ -12504,7 +12504,7 @@
     <row r="320">
       <c r="A320" s="14" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Roles as ClearOps_Role</t>
         </is>
       </c>
       <c r="B320" s="14" t="inlineStr">
@@ -12533,7 +12533,7 @@
     <row r="321">
       <c r="A321" s="14" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Roles as ClearOps_Role</t>
         </is>
       </c>
       <c r="B321" s="16" t="inlineStr">
@@ -12562,7 +12562,7 @@
     <row r="322">
       <c r="A322" s="14" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Roles as ClearOps_Role</t>
         </is>
       </c>
       <c r="B322" s="14" t="inlineStr">
@@ -12591,7 +12591,7 @@
     <row r="323">
       <c r="A323" s="14" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Roles as ClearOps_Role</t>
         </is>
       </c>
       <c r="B323" s="14" t="inlineStr">
@@ -12620,7 +12620,7 @@
     <row r="324">
       <c r="A324" s="14" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Roles as ClearOps_Role</t>
         </is>
       </c>
       <c r="B324" s="14" t="inlineStr">
@@ -12649,7 +12649,7 @@
     <row r="325">
       <c r="A325" s="14" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Roles as ClearOps_Role</t>
         </is>
       </c>
       <c r="B325" s="14" t="inlineStr">
@@ -12678,7 +12678,7 @@
     <row r="326">
       <c r="A326" s="14" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t>Pages as ClearOps_Page</t>
         </is>
       </c>
       <c r="B326" s="14" t="inlineStr">
@@ -12711,7 +12711,7 @@
     <row r="327">
       <c r="A327" s="14" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t>Pages as ClearOps_Page</t>
         </is>
       </c>
       <c r="B327" s="14" t="inlineStr">
@@ -12740,7 +12740,7 @@
     <row r="328">
       <c r="A328" s="14" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t>Pages as ClearOps_Page</t>
         </is>
       </c>
       <c r="B328" s="14" t="inlineStr">
@@ -12769,7 +12769,7 @@
     <row r="329">
       <c r="A329" s="14" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t>Pages as ClearOps_Page</t>
         </is>
       </c>
       <c r="B329" s="16" t="inlineStr">
@@ -12798,7 +12798,7 @@
     <row r="330">
       <c r="A330" s="14" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t>Pages as ClearOps_Page</t>
         </is>
       </c>
       <c r="B330" s="14" t="inlineStr">
@@ -12827,7 +12827,7 @@
     <row r="331">
       <c r="A331" s="14" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t>Pages as ClearOps_Page</t>
         </is>
       </c>
       <c r="B331" s="14" t="inlineStr">
@@ -12856,7 +12856,7 @@
     <row r="332">
       <c r="A332" s="14" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t>Pages as ClearOps_Page</t>
         </is>
       </c>
       <c r="B332" s="14" t="inlineStr">
@@ -12885,7 +12885,7 @@
     <row r="333">
       <c r="A333" s="14" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t>Pages as ClearOps_Page</t>
         </is>
       </c>
       <c r="B333" s="14" t="inlineStr">
@@ -12914,7 +12914,7 @@
     <row r="334">
       <c r="A334" s="14" t="inlineStr">
         <is>
-          <t>Access Levels</t>
+          <t>Access Levels as ClearOps_Access</t>
         </is>
       </c>
       <c r="B334" s="14" t="inlineStr">
@@ -12947,7 +12947,7 @@
     <row r="335">
       <c r="A335" s="14" t="inlineStr">
         <is>
-          <t>Access Levels</t>
+          <t>Access Levels as ClearOps_Access</t>
         </is>
       </c>
       <c r="B335" s="15" t="inlineStr">
@@ -12976,7 +12976,7 @@
     <row r="336">
       <c r="A336" s="14" t="inlineStr">
         <is>
-          <t>Access Levels</t>
+          <t>Access Levels as ClearOps_Access</t>
         </is>
       </c>
       <c r="B336" s="14" t="inlineStr">
@@ -13005,7 +13005,7 @@
     <row r="337">
       <c r="A337" s="14" t="inlineStr">
         <is>
-          <t>Access Levels</t>
+          <t>Access Levels as ClearOps_Access</t>
         </is>
       </c>
       <c r="B337" s="14" t="inlineStr">
@@ -13034,7 +13034,7 @@
     <row r="338">
       <c r="A338" s="14" t="inlineStr">
         <is>
-          <t>Access Levels</t>
+          <t>Access Levels as ClearOps_Access</t>
         </is>
       </c>
       <c r="B338" s="14" t="inlineStr">
@@ -13063,7 +13063,7 @@
     <row r="339">
       <c r="A339" s="14" t="inlineStr">
         <is>
-          <t>Access Levels</t>
+          <t>Access Levels as ClearOps_Access</t>
         </is>
       </c>
       <c r="B339" s="14" t="inlineStr">
@@ -13092,7 +13092,7 @@
     <row r="340">
       <c r="A340" s="14" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Permissions as ClearOps_Permission</t>
         </is>
       </c>
       <c r="B340" s="14" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="E340" s="14" t="inlineStr">
         <is>
-          <t>Unique number of each row in Permissions</t>
+          <t>Unique number of each row in Permissions as ClearOps_Permission</t>
         </is>
       </c>
       <c r="F340" s="14" t="inlineStr">
@@ -13125,7 +13125,7 @@
     <row r="341">
       <c r="A341" s="14" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Permissions as ClearOps_Permission</t>
         </is>
       </c>
       <c r="B341" s="14" t="inlineStr">
@@ -13155,14 +13155,14 @@
       </c>
       <c r="G341" s="14" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Roles as ClearOps_Role</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="14" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Permissions as ClearOps_Permission</t>
         </is>
       </c>
       <c r="B342" s="14" t="inlineStr">
@@ -13192,14 +13192,14 @@
       </c>
       <c r="G342" s="14" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t>Pages as ClearOps_Page</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="14" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Permissions as ClearOps_Permission</t>
         </is>
       </c>
       <c r="B343" s="14" t="inlineStr">
@@ -13229,14 +13229,14 @@
       </c>
       <c r="G343" s="14" t="inlineStr">
         <is>
-          <t>Access Levels</t>
+          <t>Access Levels as ClearOps_Access</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="14" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Permissions as ClearOps_Permission</t>
         </is>
       </c>
       <c r="B344" s="14" t="inlineStr">
@@ -13265,7 +13265,7 @@
     <row r="345">
       <c r="A345" s="14" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Permissions as ClearOps_Permission</t>
         </is>
       </c>
       <c r="B345" s="14" t="inlineStr">
@@ -13294,7 +13294,7 @@
     <row r="346">
       <c r="A346" s="14" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Permissions as ClearOps_Permission</t>
         </is>
       </c>
       <c r="B346" s="14" t="inlineStr">
@@ -13323,7 +13323,7 @@
     <row r="347">
       <c r="A347" s="14" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Permissions as ClearOps_Permission</t>
         </is>
       </c>
       <c r="B347" s="14" t="inlineStr">
@@ -13352,7 +13352,7 @@
     <row r="348">
       <c r="A348" s="14" t="inlineStr">
         <is>
-          <t>Application Users</t>
+          <t>Application Users as ClearOps_Users</t>
         </is>
       </c>
       <c r="B348" s="15" t="inlineStr">
@@ -13385,7 +13385,7 @@
     <row r="349">
       <c r="A349" s="14" t="inlineStr">
         <is>
-          <t>Application Users</t>
+          <t>Application Users as ClearOps_Users</t>
         </is>
       </c>
       <c r="B349" s="14" t="inlineStr">
@@ -13415,14 +13415,14 @@
       </c>
       <c r="G349" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="14" t="inlineStr">
         <is>
-          <t>Application Users</t>
+          <t>Application Users as ClearOps_Users</t>
         </is>
       </c>
       <c r="B350" s="14" t="inlineStr">
@@ -13452,14 +13452,14 @@
       </c>
       <c r="G350" s="14" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Roles as ClearOps_Role</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="14" t="inlineStr">
         <is>
-          <t>Application Users</t>
+          <t>Application Users as ClearOps_Users</t>
         </is>
       </c>
       <c r="B351" s="16" t="inlineStr">
@@ -13488,7 +13488,7 @@
     <row r="352">
       <c r="A352" s="14" t="inlineStr">
         <is>
-          <t>Application Users</t>
+          <t>Application Users as ClearOps_Users</t>
         </is>
       </c>
       <c r="B352" s="14" t="inlineStr">
@@ -13517,7 +13517,7 @@
     <row r="353">
       <c r="A353" s="14" t="inlineStr">
         <is>
-          <t>Application Users</t>
+          <t>Application Users as ClearOps_Users</t>
         </is>
       </c>
       <c r="B353" s="14" t="inlineStr">
@@ -13546,7 +13546,7 @@
     <row r="354">
       <c r="A354" s="14" t="inlineStr">
         <is>
-          <t>Application Users</t>
+          <t>Application Users as ClearOps_Users</t>
         </is>
       </c>
       <c r="B354" s="14" t="inlineStr">
@@ -13575,7 +13575,7 @@
     <row r="355">
       <c r="A355" s="14" t="inlineStr">
         <is>
-          <t>Application Users</t>
+          <t>Application Users as ClearOps_Users</t>
         </is>
       </c>
       <c r="B355" s="14" t="inlineStr">
@@ -13604,7 +13604,7 @@
     <row r="356">
       <c r="A356" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link</t>
+          <t>Single Sign-On Link as ClearOps_Login</t>
         </is>
       </c>
       <c r="B356" s="16" t="inlineStr">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="E356" s="14" t="inlineStr">
         <is>
-          <t>Unique number of each row in Single Sign-On Link [Was missing – table had no PK]</t>
+          <t>Unique number of each row in Single Sign-On Link as ClearOps_Login [Was missing – table had no PK]</t>
         </is>
       </c>
       <c r="F356" s="14" t="inlineStr">
@@ -13637,7 +13637,7 @@
     <row r="357">
       <c r="A357" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link</t>
+          <t>Single Sign-On Link as ClearOps_Login</t>
         </is>
       </c>
       <c r="B357" s="14" t="inlineStr">
@@ -13667,14 +13667,14 @@
       </c>
       <c r="G357" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link</t>
+          <t>Single Sign-On Link as ClearOps_Login</t>
         </is>
       </c>
       <c r="B358" s="15" t="inlineStr">
@@ -13703,7 +13703,7 @@
     <row r="359">
       <c r="A359" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link</t>
+          <t>Single Sign-On Link as ClearOps_Login</t>
         </is>
       </c>
       <c r="B359" s="14" t="inlineStr">
@@ -13732,7 +13732,7 @@
     <row r="360">
       <c r="A360" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link</t>
+          <t>Single Sign-On Link as ClearOps_Login</t>
         </is>
       </c>
       <c r="B360" s="14" t="inlineStr">
@@ -13761,7 +13761,7 @@
     <row r="361">
       <c r="A361" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link</t>
+          <t>Single Sign-On Link as ClearOps_Login</t>
         </is>
       </c>
       <c r="B361" s="14" t="inlineStr">
@@ -13790,7 +13790,7 @@
     <row r="362">
       <c r="A362" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link</t>
+          <t>Single Sign-On Link as ClearOps_Login</t>
         </is>
       </c>
       <c r="B362" s="14" t="inlineStr">
@@ -13819,7 +13819,7 @@
     <row r="363">
       <c r="A363" s="14" t="inlineStr">
         <is>
-          <t>Login History</t>
+          <t>Login History as ClearOps_UserLogin</t>
         </is>
       </c>
       <c r="B363" s="16" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="E363" s="14" t="inlineStr">
         <is>
-          <t>Unique number of each row in Login History [Was missing – no PK]</t>
+          <t>Unique number of each row in Login History as ClearOps_UserLogin [Was missing – no PK]</t>
         </is>
       </c>
       <c r="F363" s="14" t="inlineStr">
@@ -13852,7 +13852,7 @@
     <row r="364">
       <c r="A364" s="14" t="inlineStr">
         <is>
-          <t>Login History</t>
+          <t>Login History as ClearOps_UserLogin</t>
         </is>
       </c>
       <c r="B364" s="14" t="inlineStr">
@@ -13882,14 +13882,14 @@
       </c>
       <c r="G364" s="14" t="inlineStr">
         <is>
-          <t>Application Users</t>
+          <t>Application Users as ClearOps_Users</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="14" t="inlineStr">
         <is>
-          <t>Login History</t>
+          <t>Login History as ClearOps_UserLogin</t>
         </is>
       </c>
       <c r="B365" s="15" t="inlineStr">
@@ -13918,7 +13918,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Login History</t>
+          <t>Login History as ClearOps_UserLogin</t>
         </is>
       </c>
       <c r="B366" s="14" t="inlineStr">
@@ -14010,12 +14010,12 @@
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>Each People (HR master list) row points to one Job Grades row</t>
+          <t>Each People (HR master list) as Employee_Master row points to one Job Grades as Grades row</t>
         </is>
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="E4" s="16" t="inlineStr">
@@ -14037,12 +14037,12 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>Each People (HR master list) row points to one Lines of Business row</t>
+          <t>Each People (HR master list) as Employee_Master row points to one Lines of Business as LOB row</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Lines of Business</t>
+          <t>Lines of Business as LOB</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
@@ -14064,12 +14064,12 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>Each People (HR master list) row points to one Countries row</t>
+          <t>Each People (HR master list) as Employee_Master row points to one Countries as ClearOps_Country row</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>Countries</t>
+          <t>Countries as ClearOps_Country</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -14091,12 +14091,12 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>Each Exchange Rates row points to one Currencies row</t>
+          <t>Each Exchange Rates as ClearOps_FXRates row points to one Currencies as ClearOps_Currency row</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -14118,12 +14118,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>Each Exchange Rates row points to one Currencies row</t>
+          <t>Each Exchange Rates as ClearOps_FXRates row points to one Currencies as ClearOps_Currency row</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -14133,7 +14133,7 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -14145,12 +14145,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>Each Rate Card row points to one Customers row</t>
+          <t>Each Rate Card as ClearOps_RateCard row points to one Customers as ClearOps_Customer row</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Customers as ClearOps_Customer</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -14172,12 +14172,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>Each Rate Card row points to one Job Grades row</t>
+          <t>Each Rate Card as ClearOps_RateCard row points to one Job Grades as Grades row</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
@@ -14199,12 +14199,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>Each Rate Card row points to one Currencies row</t>
+          <t>Each Rate Card as ClearOps_RateCard row points to one Currencies as ClearOps_Currency row</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
@@ -14226,12 +14226,12 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Each Rate Card row points to one Countries row</t>
+          <t>Each Rate Card as ClearOps_RateCard row points to one Countries as ClearOps_Country row</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Countries</t>
+          <t>Countries as ClearOps_Country</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
@@ -14253,12 +14253,12 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>Each Holidays row points to one Countries row</t>
+          <t>Each Holidays as ClearOps_Holiday row points to one Countries as ClearOps_Country row</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Holidays as ClearOps_Holiday</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Countries</t>
+          <t>Countries as ClearOps_Country</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
@@ -14280,12 +14280,12 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>Each Pass-through Costs row points to one Projects row</t>
+          <t>Each Pass-through Costs as ClearOps_Passthrough row points to one Projects as Project_Master row</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="E14" s="16" t="inlineStr">
@@ -14307,12 +14307,12 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>Each Pass-through Costs row points to one Project Tasks (WBS) row</t>
+          <t>Each Pass-through Costs as ClearOps_Passthrough row points to one Project Tasks (WBS) as ClearOps_ProjectWBS row</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -14334,12 +14334,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>Each Pass-through Costs row points to one Currencies row</t>
+          <t>Each Pass-through Costs as ClearOps_Passthrough row points to one Currencies as ClearOps_Currency row</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -14349,7 +14349,7 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
@@ -14361,12 +14361,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>Each Resources (bookable people) row points to one People (HR master list) row</t>
+          <t>Each Resources (bookable people) as Resources row points to one People (HR master list) as Employee_Master row</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="E17" s="16" t="inlineStr">
@@ -14388,12 +14388,12 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>Each Resources (bookable people) row points to one Job Grades row</t>
+          <t>Each Resources (bookable people) as Resources row points to one Job Grades as Grades row</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="E18" s="16" t="inlineStr">
@@ -14415,12 +14415,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>Each Resources (bookable people) row points to one Lines of Business row</t>
+          <t>Each Resources (bookable people) as Resources row points to one Lines of Business as LOB row</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Lines of Business</t>
+          <t>Lines of Business as LOB</t>
         </is>
       </c>
       <c r="E19" s="16" t="inlineStr">
@@ -14442,12 +14442,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Each Teams row points to one Resources (bookable people) row</t>
+          <t>Each Teams as ClearOps_Teams row points to one Resources (bookable people) as Resources row</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
@@ -14469,12 +14469,12 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Each Teams row points to one Resources (bookable people) row</t>
+          <t>Each Teams as ClearOps_Teams row points to one Resources (bookable people) as Resources row</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
@@ -14484,7 +14484,7 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -14496,12 +14496,12 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>Each Team Members row points to one Teams row</t>
+          <t>Each Team Members as ClearOps_TeamMember row points to one Teams as ClearOps_Teams row</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>Team Members as ClearOps_TeamMember</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
@@ -14523,12 +14523,12 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>Each Team Members row points to one Resources (bookable people) row</t>
+          <t>Each Team Members as ClearOps_TeamMember row points to one Resources (bookable people) as Resources row</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>Team Members as ClearOps_TeamMember</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
@@ -14550,12 +14550,12 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>Each Time Off row points to one People (HR master list) row</t>
+          <t>Each Time Off as ClearOps_TimeOff row points to one People (HR master list) as Employee_Master row</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>Time Off</t>
+          <t>Time Off as ClearOps_TimeOff</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="E24" s="16" t="inlineStr">
@@ -14577,12 +14577,12 @@
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>Each Time Planner row points to one Projects row</t>
+          <t>Each Time Planner as ClearOps_ProjectTimePlanner row points to one Projects as Project_Master row</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -14604,12 +14604,12 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>Each Time Planner row points to one Project Tasks (WBS) row</t>
+          <t>Each Time Planner as ClearOps_ProjectTimePlanner row points to one Project Tasks (WBS) as ClearOps_ProjectWBS row</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="E26" s="16" t="inlineStr">
@@ -14631,12 +14631,12 @@
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Each Time Planner row points to one Resources (bookable people) row</t>
+          <t>Each Time Planner as ClearOps_ProjectTimePlanner row points to one Resources (bookable people) as Resources row</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="E27" s="16" t="inlineStr">
@@ -14658,12 +14658,12 @@
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>Each Projects row points to one Customers row</t>
+          <t>Each Projects as Project_Master row points to one Customers as ClearOps_Customer row</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
@@ -14673,7 +14673,7 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Customers as ClearOps_Customer</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -14685,12 +14685,12 @@
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>Each Projects row points to one Lines of Business row</t>
+          <t>Each Projects as Project_Master row points to one Lines of Business as LOB row</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>Lines of Business</t>
+          <t>Lines of Business as LOB</t>
         </is>
       </c>
       <c r="E29" s="16" t="inlineStr">
@@ -14712,12 +14712,12 @@
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Each Projects row points to one Currencies row</t>
+          <t>Each Projects as Project_Master row points to one Currencies as ClearOps_Currency row</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -14739,12 +14739,12 @@
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Each Projects row points to one Currencies row</t>
+          <t>Each Projects as Project_Master row points to one Currencies as ClearOps_Currency row</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -14766,12 +14766,12 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>Each Projects row points to one People (HR master list) row</t>
+          <t>Each Projects as Project_Master row points to one People (HR master list) as Employee_Master row</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="E32" s="16" t="inlineStr">
@@ -14793,12 +14793,12 @@
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>Each Projects row points to one People (HR master list) row</t>
+          <t>Each Projects as Project_Master row points to one People (HR master list) as Employee_Master row</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="E33" s="16" t="inlineStr">
@@ -14820,12 +14820,12 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Each Projects row points to one People (HR master list) row</t>
+          <t>Each Projects as Project_Master row points to one People (HR master list) as Employee_Master row</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="E34" s="16" t="inlineStr">
@@ -14847,12 +14847,12 @@
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>Each Projects row points to one People (HR master list) row</t>
+          <t>Each Projects as Project_Master row points to one People (HR master list) as Employee_Master row</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
@@ -14874,12 +14874,12 @@
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>Each Projects row points to one People (HR master list) row</t>
+          <t>Each Projects as Project_Master row points to one People (HR master list) as Employee_Master row</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="E36" s="16" t="inlineStr">
@@ -14901,12 +14901,12 @@
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>Each Projects row points to one People (HR master list) row</t>
+          <t>Each Projects as Project_Master row points to one People (HR master list) as Employee_Master row</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="E37" s="16" t="inlineStr">
@@ -14928,12 +14928,12 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Each Project Tasks (WBS) row points to one Projects row</t>
+          <t>Each Project Tasks (WBS) as ClearOps_ProjectWBS row points to one Projects as Project_Master row</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
@@ -14943,7 +14943,7 @@
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="E38" s="16" t="inlineStr">
@@ -14955,12 +14955,12 @@
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>Each Project Tasks (WBS) row points to one Project Tasks (WBS) row</t>
+          <t>Each Project Tasks (WBS) as ClearOps_ProjectWBS row points to one Project Tasks (WBS) as ClearOps_ProjectWBS row</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -14982,12 +14982,12 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Each Project Tasks (WBS) row points to one Project Tasks (WBS) row</t>
+          <t>Each Project Tasks (WBS) as ClearOps_ProjectWBS row points to one Project Tasks (WBS) as ClearOps_ProjectWBS row</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="E40" s="16" t="inlineStr">
@@ -15009,12 +15009,12 @@
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Each Project Estimates row points to one Projects row</t>
+          <t>Each Project Estimates as ClearOps_ProjectEstimator row points to one Projects as Project_Master row</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="C41" s="14" t="inlineStr">
@@ -15024,7 +15024,7 @@
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="E41" s="16" t="inlineStr">
@@ -15036,12 +15036,12 @@
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>Each Project Estimates row points to one Project Tasks (WBS) row</t>
+          <t>Each Project Estimates as ClearOps_ProjectEstimator row points to one Project Tasks (WBS) as ClearOps_ProjectWBS row</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="E42" s="16" t="inlineStr">
@@ -15063,12 +15063,12 @@
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>Each Project Estimates row points to one Job Grades row</t>
+          <t>Each Project Estimates as ClearOps_ProjectEstimator row points to one Job Grades as Grades row</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -15090,12 +15090,12 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>Each Project Finance Settings row points to one Projects row</t>
+          <t>Each Project Finance Settings as ClearOps_ProjectSettings row points to one Projects as Project_Master row</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="E44" s="16" t="inlineStr">
@@ -15117,12 +15117,12 @@
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>Each Project Assignments (grid rows) row points to one Projects row</t>
+          <t>Each Project Assignments (grid rows) as ClearOps_ProjectSTP row points to one Projects as Project_Master row</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="D45" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="E45" s="16" t="inlineStr">
@@ -15144,12 +15144,12 @@
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Each Project Assignments (grid rows) row points to one Project Tasks (WBS) row</t>
+          <t>Each Project Assignments (grid rows) as ClearOps_ProjectSTP row points to one Project Tasks (WBS) as ClearOps_ProjectWBS row</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="E46" s="16" t="inlineStr">
@@ -15171,12 +15171,12 @@
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>Each Project Assignments (grid rows) row points to one Resources (bookable people) row</t>
+          <t>Each Project Assignments (grid rows) as ClearOps_ProjectSTP row points to one Resources (bookable people) as Resources row</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>Resources (bookable people)</t>
+          <t>Resources (bookable people) as Resources</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -15198,12 +15198,12 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>Each Project Assignments (grid rows) row points to one Rate Card row</t>
+          <t>Each Project Assignments (grid rows) as ClearOps_ProjectSTP row points to one Rate Card as ClearOps_RateCard row</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -15225,12 +15225,12 @@
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>Each Monthly Hours (grid cells) row points to one Project Assignments (grid rows) row</t>
+          <t>Each Monthly Hours (grid cells) as ClearOps_ProjectSTP_Month row points to one Project Assignments (grid rows) as ClearOps_ProjectSTP row</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Monthly Hours (grid cells)</t>
+          <t>Monthly Hours (grid cells) as ClearOps_ProjectSTP_Month</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="D49" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -15252,12 +15252,12 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>Each Integration Run Log row points to one Integration Status row</t>
+          <t>Each Integration Run Log as ClearOps_Logs row points to one Integration Status as Admin_IntegrationStatus row</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>Integration Status</t>
+          <t>Integration Status as Admin_IntegrationStatus</t>
         </is>
       </c>
       <c r="E50" s="16" t="inlineStr">
@@ -15279,12 +15279,12 @@
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>Each Permissions row points to one Roles row</t>
+          <t>Each Permissions as ClearOps_Permission row points to one Roles as ClearOps_Role row</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Permissions as ClearOps_Permission</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Roles as ClearOps_Role</t>
         </is>
       </c>
       <c r="E51" s="16" t="inlineStr">
@@ -15306,12 +15306,12 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>Each Permissions row points to one Pages row</t>
+          <t>Each Permissions as ClearOps_Permission row points to one Pages as ClearOps_Page row</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Permissions as ClearOps_Permission</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
@@ -15321,7 +15321,7 @@
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t>Pages as ClearOps_Page</t>
         </is>
       </c>
       <c r="E52" s="16" t="inlineStr">
@@ -15333,12 +15333,12 @@
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>Each Permissions row points to one Access Levels row</t>
+          <t>Each Permissions as ClearOps_Permission row points to one Access Levels as ClearOps_Access row</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Permissions as ClearOps_Permission</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -15348,7 +15348,7 @@
       </c>
       <c r="D53" s="14" t="inlineStr">
         <is>
-          <t>Access Levels</t>
+          <t>Access Levels as ClearOps_Access</t>
         </is>
       </c>
       <c r="E53" s="16" t="inlineStr">
@@ -15360,12 +15360,12 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Each Application Users row points to one People (HR master list) row</t>
+          <t>Each Application Users as ClearOps_Users row points to one People (HR master list) as Employee_Master row</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Application Users</t>
+          <t>Application Users as ClearOps_Users</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="E54" s="16" t="inlineStr">
@@ -15387,12 +15387,12 @@
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>Each Application Users row points to one Roles row</t>
+          <t>Each Application Users as ClearOps_Users row points to one Roles as ClearOps_Role row</t>
         </is>
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Application Users</t>
+          <t>Application Users as ClearOps_Users</t>
         </is>
       </c>
       <c r="C55" s="14" t="inlineStr">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="D55" s="14" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Roles as ClearOps_Role</t>
         </is>
       </c>
       <c r="E55" s="16" t="inlineStr">
@@ -15414,12 +15414,12 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>Each Single Sign-On Link row points to one People (HR master list) row</t>
+          <t>Each Single Sign-On Link as ClearOps_Login row points to one People (HR master list) as Employee_Master row</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link</t>
+          <t>Single Sign-On Link as ClearOps_Login</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
@@ -15429,7 +15429,7 @@
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="E56" s="16" t="inlineStr">
@@ -15441,12 +15441,12 @@
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
-          <t>Each Login History row points to one Application Users row</t>
+          <t>Each Login History as ClearOps_UserLogin row points to one Application Users as ClearOps_Users row</t>
         </is>
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Login History</t>
+          <t>Login History as ClearOps_UserLogin</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="D57" s="14" t="inlineStr">
         <is>
-          <t>Application Users</t>
+          <t>Application Users as ClearOps_Users</t>
         </is>
       </c>
       <c r="E57" s="16" t="inlineStr">
@@ -15475,7 +15475,7 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>Team Members as ClearOps_TeamMember</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
@@ -15490,7 +15490,7 @@
     <row r="61">
       <c r="A61" s="14" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Permissions as ClearOps_Permission</t>
         </is>
       </c>
       <c r="B61" s="14" t="inlineStr">
@@ -15505,7 +15505,7 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
@@ -15520,7 +15520,7 @@
     <row r="63">
       <c r="A63" s="14" t="inlineStr">
         <is>
-          <t>Monthly Hours (grid cells)</t>
+          <t>Monthly Hours (grid cells) as ClearOps_ProjectSTP_Month</t>
         </is>
       </c>
       <c r="B63" s="14" t="inlineStr">
@@ -16260,7 +16260,7 @@
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B4" s="14" t="inlineStr">
@@ -16282,7 +16282,7 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
@@ -16304,7 +16304,7 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
@@ -16326,7 +16326,7 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
@@ -16348,7 +16348,7 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>People (HR master list)</t>
+          <t>People (HR master list) as Employee_Master</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
@@ -16370,7 +16370,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -16392,7 +16392,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -16414,7 +16414,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -16436,7 +16436,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -16458,7 +16458,7 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>Job Grades</t>
+          <t>Job Grades as Grades</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
@@ -16480,7 +16480,7 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>Countries</t>
+          <t>Countries as ClearOps_Country</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
@@ -16502,7 +16502,7 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>Currencies</t>
+          <t>Currencies as ClearOps_Currency</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -16524,7 +16524,7 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Customers as ClearOps_Customer</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -16546,7 +16546,7 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -16568,7 +16568,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -16590,7 +16590,7 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
@@ -16612,7 +16612,7 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Exchange Rates</t>
+          <t>Exchange Rates as ClearOps_FXRates</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -16634,7 +16634,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -16656,7 +16656,7 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
@@ -16678,7 +16678,7 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Rate Card as ClearOps_RateCard</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
@@ -16700,7 +16700,7 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Holidays as ClearOps_Holiday</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
@@ -16722,7 +16722,7 @@
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
@@ -16744,7 +16744,7 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>Pass-through Costs</t>
+          <t>Pass-through Costs as ClearOps_Passthrough</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
@@ -16766,7 +16766,7 @@
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
@@ -16788,7 +16788,7 @@
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
@@ -16810,7 +16810,7 @@
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
@@ -16832,7 +16832,7 @@
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Teams as ClearOps_Teams</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
@@ -16854,7 +16854,7 @@
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>Team Members as ClearOps_TeamMember</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
@@ -16876,7 +16876,7 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>Time Off</t>
+          <t>Time Off as ClearOps_TimeOff</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
@@ -16898,7 +16898,7 @@
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>Time Off</t>
+          <t>Time Off as ClearOps_TimeOff</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
@@ -16920,7 +16920,7 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Time Off</t>
+          <t>Time Off as ClearOps_TimeOff</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
@@ -16942,7 +16942,7 @@
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
@@ -16964,7 +16964,7 @@
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>Time Planner</t>
+          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
@@ -16986,7 +16986,7 @@
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
@@ -17008,7 +17008,7 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
@@ -17030,7 +17030,7 @@
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
@@ -17052,7 +17052,7 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
@@ -17074,7 +17074,7 @@
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
@@ -17096,7 +17096,7 @@
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
@@ -17118,7 +17118,7 @@
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Projects as Project_Master</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
@@ -17140,7 +17140,7 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
@@ -17162,7 +17162,7 @@
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
@@ -17184,7 +17184,7 @@
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
@@ -17206,7 +17206,7 @@
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
@@ -17228,7 +17228,7 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
@@ -17250,7 +17250,7 @@
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS)</t>
+          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
@@ -17272,7 +17272,7 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
@@ -17294,7 +17294,7 @@
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
@@ -17316,7 +17316,7 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates</t>
+          <t>Project Estimates as ClearOps_ProjectEstimator</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
@@ -17338,7 +17338,7 @@
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
@@ -17360,7 +17360,7 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings</t>
+          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
@@ -17382,7 +17382,7 @@
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B55" s="14" t="inlineStr">
@@ -17404,7 +17404,7 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
@@ -17426,7 +17426,7 @@
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B57" s="14" t="inlineStr">
@@ -17448,7 +17448,7 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
@@ -17470,7 +17470,7 @@
     <row r="59">
       <c r="A59" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B59" s="14" t="inlineStr">
@@ -17492,7 +17492,7 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
@@ -17514,7 +17514,7 @@
     <row r="61">
       <c r="A61" s="14" t="inlineStr">
         <is>
-          <t>Project Assignments (grid rows)</t>
+          <t>Project Assignments (grid rows) as ClearOps_ProjectSTP</t>
         </is>
       </c>
       <c r="B61" s="14" t="inlineStr">
@@ -17536,7 +17536,7 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>Monthly Hours (grid cells)</t>
+          <t>Monthly Hours (grid cells) as ClearOps_ProjectSTP_Month</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
@@ -17558,7 +17558,7 @@
     <row r="63">
       <c r="A63" s="14" t="inlineStr">
         <is>
-          <t>Project Forecasting (OLD)</t>
+          <t>Project Forecasting (OLD) as ClearOps_ProjectForecasting</t>
         </is>
       </c>
       <c r="B63" s="14" t="inlineStr">
@@ -17580,7 +17580,7 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>Integration Status</t>
+          <t>Integration Status as Admin_IntegrationStatus</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
@@ -17602,7 +17602,7 @@
     <row r="65">
       <c r="A65" s="14" t="inlineStr">
         <is>
-          <t>Integration Status</t>
+          <t>Integration Status as Admin_IntegrationStatus</t>
         </is>
       </c>
       <c r="B65" s="14" t="inlineStr">
@@ -17624,7 +17624,7 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
@@ -17646,7 +17646,7 @@
     <row r="67">
       <c r="A67" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B67" s="14" t="inlineStr">
@@ -17668,7 +17668,7 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
@@ -17690,7 +17690,7 @@
     <row r="69">
       <c r="A69" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B69" s="14" t="inlineStr">
@@ -17712,7 +17712,7 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
@@ -17734,7 +17734,7 @@
     <row r="71">
       <c r="A71" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B71" s="14" t="inlineStr">
@@ -17756,7 +17756,7 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
@@ -17778,7 +17778,7 @@
     <row r="73">
       <c r="A73" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B73" s="14" t="inlineStr">
@@ -17800,7 +17800,7 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
@@ -17822,7 +17822,7 @@
     <row r="75">
       <c r="A75" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log</t>
+          <t>Integration Run Log as ClearOps_Logs</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
@@ -17844,7 +17844,7 @@
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Roles as ClearOps_Role</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
@@ -17866,7 +17866,7 @@
     <row r="77">
       <c r="A77" s="14" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t>Pages as ClearOps_Page</t>
         </is>
       </c>
       <c r="B77" s="14" t="inlineStr">
@@ -17888,7 +17888,7 @@
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>Access Levels</t>
+          <t>Access Levels as ClearOps_Access</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
@@ -17910,7 +17910,7 @@
     <row r="79">
       <c r="A79" s="14" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Permissions as ClearOps_Permission</t>
         </is>
       </c>
       <c r="B79" s="14" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>Application Users</t>
+          <t>Application Users as ClearOps_Users</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
@@ -17954,7 +17954,7 @@
     <row r="81">
       <c r="A81" s="14" t="inlineStr">
         <is>
-          <t>Application Users</t>
+          <t>Application Users as ClearOps_Users</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
@@ -17976,7 +17976,7 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link</t>
+          <t>Single Sign-On Link as ClearOps_Login</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
@@ -17998,7 +17998,7 @@
     <row r="83">
       <c r="A83" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link</t>
+          <t>Single Sign-On Link as ClearOps_Login</t>
         </is>
       </c>
       <c r="B83" s="14" t="inlineStr">
@@ -18020,7 +18020,7 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link</t>
+          <t>Single Sign-On Link as ClearOps_Login</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
@@ -18042,7 +18042,7 @@
     <row r="85">
       <c r="A85" s="14" t="inlineStr">
         <is>
-          <t>Login History</t>
+          <t>Login History as ClearOps_UserLogin</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
@@ -18064,7 +18064,7 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>Login History</t>
+          <t>Login History as ClearOps_UserLogin</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
@@ -18086,7 +18086,7 @@
     <row r="87">
       <c r="A87" s="14" t="inlineStr">
         <is>
-          <t>Login History</t>
+          <t>Login History as ClearOps_UserLogin</t>
         </is>
       </c>
       <c r="B87" s="14" t="inlineStr">
@@ -18108,7 +18108,7 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>Roles &amp; Permissions (OLD sheet)</t>
+          <t>Roles &amp; Permissions (OLD sheet) as RolesandPermissions</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">

--- a/ClearOps_Database_Mapped.xlsx
+++ b/ClearOps_Database_Mapped.xlsx
@@ -954,7 +954,7 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Time Off as ClearOps_TimeOff</t>
+          <t>Time Off as TimeOff(WD)</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -1185,7 +1185,7 @@
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
@@ -1195,14 +1195,14 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS, Projects as Project_Master</t>
+          <t>Project Tasks (WBS) as ProjectWBS, Projects as Project_Master</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
@@ -1212,14 +1212,14 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Job Grades as Grades, Project Tasks (WBS) as ClearOps_ProjectWBS, Projects as Project_Master</t>
+          <t>Job Grades as Grades, Project Tasks (WBS) as ProjectWBS, Projects as Project_Master</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
@@ -1246,14 +1246,14 @@
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Currencies as ClearOps_Currency, Project Tasks (WBS) as ClearOps_ProjectWBS, Projects as Project_Master</t>
+          <t>Currencies as ClearOps_Currency, Project Tasks (WBS) as ProjectWBS, Projects as Project_Master</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS, Projects as Project_Master, Resources (bookable people) as Resources</t>
+          <t>Project Tasks (WBS) as ProjectWBS, Projects as Project_Master, Resources (bookable people) as Resources</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS, Projects as Project_Master, Rate Card as ClearOps_RateCard, Resources (bookable people) as Resources</t>
+          <t>Project Tasks (WBS) as ProjectWBS, Projects as Project_Master, Rate Card as ClearOps_RateCard, Resources (bookable people) as Resources</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>Access Levels as ClearOps_Access</t>
+          <t>Access Levels as ClearOpps_Access_table</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>Access Levels as ClearOps_Access, Pages as ClearOps_Page, Roles as ClearOps_Role</t>
+          <t>Access Levels as ClearOpps_Access_table, Pages as ClearOps_Page, Roles as ClearOps_Role</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
     <row r="47">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>Single Sign-On Link as ClearOps_Login</t>
+          <t>Single Sign-On Link as ClearOps_login</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
@@ -1458,7 +1458,7 @@
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>Login History as ClearOps_UserLogin</t>
+          <t>Login History as UserLogin</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
@@ -1501,7 +1501,7 @@
     <row r="52">
       <c r="A52" s="15" t="inlineStr">
         <is>
-          <t>Integration Status as Admin_IntegrationStatus</t>
+          <t>Integration Status as Admin_Integration_Status</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
@@ -1518,7 +1518,7 @@
     <row r="53">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
-          <t>Integration Status as Admin_IntegrationStatus</t>
+          <t>Integration Status as Admin_Integration_Status</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
         <is>
-          <t>Project Forecasting (OLD) as ClearOps_ProjectForecasting</t>
+          <t>Project Forecasting (OLD) as Project_Forecasting</t>
         </is>
       </c>
       <c r="B57" s="14" t="inlineStr">
@@ -1578,7 +1578,7 @@
     <row r="58">
       <c r="A58" s="17" t="inlineStr">
         <is>
-          <t>Roles &amp; Permissions (OLD sheet) as RolesandPermissions</t>
+          <t>Roles &amp; Permissions (OLD sheet) as ClearOps_RolesandPermissions</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Time Off as ClearOps_TimeOff</t>
+          <t>Time Off as TimeOff(WD)</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>ClearOps_TimeOff</t>
+          <t>TimeOff(WD)</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>ClearOps_ProjectTimePlanner</t>
+          <t>ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>ClearOps_ProjectWBS</t>
+          <t>ProjectWBS</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>ClearOps_ProjectEstimator</t>
+          <t>Project_Estimator</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>ClearOps_ProjectSettings</t>
+          <t>Project_Settings</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Project Forecasting (OLD) as ClearOps_ProjectForecasting</t>
+          <t>Project Forecasting (OLD) as Project_Forecasting</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>ClearOps_ProjectForecasting</t>
+          <t>Project_Forecasting</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>Integration Status as Admin_IntegrationStatus</t>
+          <t>Integration Status as Admin_Integration_Status</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>Admin_IntegrationStatus</t>
+          <t>Admin_Integration_Status</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>ClearOps_Logs</t>
+          <t>Logs_table</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Access Levels as ClearOps_Access</t>
+          <t>Access Levels as ClearOpps_Access_table</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>ClearOps_Access</t>
+          <t>ClearOpps_Access_table</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link as ClearOps_Login</t>
+          <t>Single Sign-On Link as ClearOps_login</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>ClearOps_Login</t>
+          <t>ClearOps_login</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Login History as ClearOps_UserLogin</t>
+          <t>Login History as UserLogin</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>ClearOps_UserLogin</t>
+          <t>UserLogin</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Roles &amp; Permissions (OLD sheet) as RolesandPermissions</t>
+          <t>Roles &amp; Permissions (OLD sheet) as ClearOps_RolesandPermissions</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>RolesandPermissions</t>
+          <t>ClearOps_RolesandPermissions</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="G118" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
         <is>
-          <t>Time Off as ClearOps_TimeOff</t>
+          <t>Time Off as TimeOff(WD)</t>
         </is>
       </c>
       <c r="B162" s="14" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>Unique number of each row in Time Off as ClearOps_TimeOff</t>
+          <t>Unique number of each row in Time Off as TimeOff(WD)</t>
         </is>
       </c>
       <c r="F162" s="14" t="inlineStr">
@@ -7695,7 +7695,7 @@
     <row r="163">
       <c r="A163" s="14" t="inlineStr">
         <is>
-          <t>Time Off as ClearOps_TimeOff</t>
+          <t>Time Off as TimeOff(WD)</t>
         </is>
       </c>
       <c r="B163" s="14" t="inlineStr">
@@ -7732,7 +7732,7 @@
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
         <is>
-          <t>Time Off as ClearOps_TimeOff</t>
+          <t>Time Off as TimeOff(WD)</t>
         </is>
       </c>
       <c r="B164" s="14" t="inlineStr">
@@ -7761,7 +7761,7 @@
     <row r="165">
       <c r="A165" s="14" t="inlineStr">
         <is>
-          <t>Time Off as ClearOps_TimeOff</t>
+          <t>Time Off as TimeOff(WD)</t>
         </is>
       </c>
       <c r="B165" s="16" t="inlineStr">
@@ -7790,7 +7790,7 @@
     <row r="166">
       <c r="A166" s="14" t="inlineStr">
         <is>
-          <t>Time Off as ClearOps_TimeOff</t>
+          <t>Time Off as TimeOff(WD)</t>
         </is>
       </c>
       <c r="B166" s="16" t="inlineStr">
@@ -7819,7 +7819,7 @@
     <row r="167">
       <c r="A167" s="14" t="inlineStr">
         <is>
-          <t>Time Off as ClearOps_TimeOff</t>
+          <t>Time Off as TimeOff(WD)</t>
         </is>
       </c>
       <c r="B167" s="14" t="inlineStr">
@@ -7848,7 +7848,7 @@
     <row r="168">
       <c r="A168" s="14" t="inlineStr">
         <is>
-          <t>Time Off as ClearOps_TimeOff</t>
+          <t>Time Off as TimeOff(WD)</t>
         </is>
       </c>
       <c r="B168" s="14" t="inlineStr">
@@ -7877,7 +7877,7 @@
     <row r="169">
       <c r="A169" s="14" t="inlineStr">
         <is>
-          <t>Time Off as ClearOps_TimeOff</t>
+          <t>Time Off as TimeOff(WD)</t>
         </is>
       </c>
       <c r="B169" s="14" t="inlineStr">
@@ -7906,7 +7906,7 @@
     <row r="170">
       <c r="A170" s="14" t="inlineStr">
         <is>
-          <t>Time Off as ClearOps_TimeOff</t>
+          <t>Time Off as TimeOff(WD)</t>
         </is>
       </c>
       <c r="B170" s="14" t="inlineStr">
@@ -7935,7 +7935,7 @@
     <row r="171">
       <c r="A171" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B171" s="15" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
-          <t>Unique number of each row in Time Planner as ClearOps_ProjectTimePlanner [Was Project_Time_Panner_id (typo)]</t>
+          <t>Unique number of each row in Time Planner as ClearOps_Project_Time_Planner [Was Project_Time_Panner_id (typo)]</t>
         </is>
       </c>
       <c r="F171" s="14" t="inlineStr">
@@ -7968,7 +7968,7 @@
     <row r="172">
       <c r="A172" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B172" s="16" t="inlineStr">
@@ -8005,7 +8005,7 @@
     <row r="173">
       <c r="A173" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B173" s="14" t="inlineStr">
@@ -8035,14 +8035,14 @@
       </c>
       <c r="G173" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B174" s="14" t="inlineStr">
@@ -8079,7 +8079,7 @@
     <row r="175">
       <c r="A175" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B175" s="14" t="inlineStr">
@@ -8108,7 +8108,7 @@
     <row r="176">
       <c r="A176" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B176" s="14" t="inlineStr">
@@ -8137,7 +8137,7 @@
     <row r="177">
       <c r="A177" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B177" s="14" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="178">
       <c r="A178" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B178" s="14" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="179">
       <c r="A179" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B179" s="14" t="inlineStr">
@@ -8224,7 +8224,7 @@
     <row r="180">
       <c r="A180" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B180" s="14" t="inlineStr">
@@ -8253,7 +8253,7 @@
     <row r="181">
       <c r="A181" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B181" s="14" t="inlineStr">
@@ -8282,7 +8282,7 @@
     <row r="182">
       <c r="A182" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B182" s="14" t="inlineStr">
@@ -8311,7 +8311,7 @@
     <row r="183">
       <c r="A183" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B183" s="14" t="inlineStr">
@@ -8340,7 +8340,7 @@
     <row r="184">
       <c r="A184" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B184" s="14" t="inlineStr">
@@ -8369,7 +8369,7 @@
     <row r="185">
       <c r="A185" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B185" s="14" t="inlineStr">
@@ -8398,7 +8398,7 @@
     <row r="186">
       <c r="A186" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B186" s="14" t="inlineStr">
@@ -9526,7 +9526,7 @@
     <row r="222">
       <c r="A222" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B222" s="15" t="inlineStr">
@@ -9559,7 +9559,7 @@
     <row r="223">
       <c r="A223" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B223" s="14" t="inlineStr">
@@ -9596,7 +9596,7 @@
     <row r="224">
       <c r="A224" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B224" s="15" t="inlineStr">
@@ -9626,14 +9626,14 @@
       </c>
       <c r="G224" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B225" s="14" t="inlineStr">
@@ -9663,14 +9663,14 @@
       </c>
       <c r="G225" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B226" s="14" t="inlineStr">
@@ -9699,7 +9699,7 @@
     <row r="227">
       <c r="A227" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B227" s="16" t="inlineStr">
@@ -9728,7 +9728,7 @@
     <row r="228">
       <c r="A228" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B228" s="15" t="inlineStr">
@@ -9757,7 +9757,7 @@
     <row r="229">
       <c r="A229" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B229" s="14" t="inlineStr">
@@ -9786,7 +9786,7 @@
     <row r="230">
       <c r="A230" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B230" s="14" t="inlineStr">
@@ -9815,7 +9815,7 @@
     <row r="231">
       <c r="A231" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B231" s="14" t="inlineStr">
@@ -9844,7 +9844,7 @@
     <row r="232">
       <c r="A232" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B232" s="14" t="inlineStr">
@@ -9873,7 +9873,7 @@
     <row r="233">
       <c r="A233" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B233" s="14" t="inlineStr">
@@ -9902,7 +9902,7 @@
     <row r="234">
       <c r="A234" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B234" s="14" t="inlineStr">
@@ -9931,7 +9931,7 @@
     <row r="235">
       <c r="A235" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B235" s="14" t="inlineStr">
@@ -9960,7 +9960,7 @@
     <row r="236">
       <c r="A236" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B236" s="15" t="inlineStr">
@@ -9989,7 +9989,7 @@
     <row r="237">
       <c r="A237" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B237" s="15" t="inlineStr">
@@ -10018,7 +10018,7 @@
     <row r="238">
       <c r="A238" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B238" s="14" t="inlineStr">
@@ -10047,7 +10047,7 @@
     <row r="239">
       <c r="A239" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B239" s="14" t="inlineStr">
@@ -10076,7 +10076,7 @@
     <row r="240">
       <c r="A240" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B240" s="14" t="inlineStr">
@@ -10105,7 +10105,7 @@
     <row r="241">
       <c r="A241" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B241" s="14" t="inlineStr">
@@ -10134,7 +10134,7 @@
     <row r="242">
       <c r="A242" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B242" s="14" t="inlineStr">
@@ -10163,7 +10163,7 @@
     <row r="243">
       <c r="A243" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B243" s="14" t="inlineStr">
@@ -10192,7 +10192,7 @@
     <row r="244">
       <c r="A244" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B244" s="14" t="inlineStr">
@@ -10221,7 +10221,7 @@
     <row r="245">
       <c r="A245" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B245" s="14" t="inlineStr">
@@ -10250,7 +10250,7 @@
     <row r="246">
       <c r="A246" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B246" s="14" t="inlineStr">
@@ -10279,7 +10279,7 @@
     <row r="247">
       <c r="A247" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="B247" s="15" t="inlineStr">
@@ -10312,7 +10312,7 @@
     <row r="248">
       <c r="A248" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="B248" s="14" t="inlineStr">
@@ -10349,7 +10349,7 @@
     <row r="249">
       <c r="A249" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="B249" s="14" t="inlineStr">
@@ -10379,14 +10379,14 @@
       </c>
       <c r="G249" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="B250" s="15" t="inlineStr">
@@ -10423,7 +10423,7 @@
     <row r="251">
       <c r="A251" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="B251" s="14" t="inlineStr">
@@ -10452,7 +10452,7 @@
     <row r="252">
       <c r="A252" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="B252" s="14" t="inlineStr">
@@ -10481,7 +10481,7 @@
     <row r="253">
       <c r="A253" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="B253" s="14" t="inlineStr">
@@ -10510,7 +10510,7 @@
     <row r="254">
       <c r="A254" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="B254" s="14" t="inlineStr">
@@ -10539,7 +10539,7 @@
     <row r="255">
       <c r="A255" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="B255" s="14" t="inlineStr">
@@ -10568,7 +10568,7 @@
     <row r="256">
       <c r="A256" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="B256" s="14" t="inlineStr">
@@ -10597,7 +10597,7 @@
     <row r="257">
       <c r="A257" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="B257" s="14" t="inlineStr">
@@ -10626,7 +10626,7 @@
     <row r="258">
       <c r="A258" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="B258" s="14" t="inlineStr">
@@ -10655,7 +10655,7 @@
     <row r="259">
       <c r="A259" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="B259" s="14" t="inlineStr">
@@ -10684,7 +10684,7 @@
     <row r="260">
       <c r="A260" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="B260" s="14" t="inlineStr">
@@ -10713,7 +10713,7 @@
     <row r="261">
       <c r="A261" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="B261" s="14" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="E261" s="14" t="inlineStr">
         <is>
-          <t>Unique number of each row in Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Unique number of each row in Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="F261" s="14" t="inlineStr">
@@ -10746,7 +10746,7 @@
     <row r="262">
       <c r="A262" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="B262" s="14" t="inlineStr">
@@ -10783,7 +10783,7 @@
     <row r="263">
       <c r="A263" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="B263" s="14" t="inlineStr">
@@ -10812,7 +10812,7 @@
     <row r="264">
       <c r="A264" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="B264" s="14" t="inlineStr">
@@ -10841,7 +10841,7 @@
     <row r="265">
       <c r="A265" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="B265" s="14" t="inlineStr">
@@ -10870,7 +10870,7 @@
     <row r="266">
       <c r="A266" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="B266" s="14" t="inlineStr">
@@ -10899,7 +10899,7 @@
     <row r="267">
       <c r="A267" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="B267" s="14" t="inlineStr">
@@ -10928,7 +10928,7 @@
     <row r="268">
       <c r="A268" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="B268" s="14" t="inlineStr">
@@ -10957,7 +10957,7 @@
     <row r="269">
       <c r="A269" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="B269" s="14" t="inlineStr">
@@ -10986,7 +10986,7 @@
     <row r="270">
       <c r="A270" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="B270" s="14" t="inlineStr">
@@ -11015,7 +11015,7 @@
     <row r="271">
       <c r="A271" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="B271" s="14" t="inlineStr">
@@ -11044,7 +11044,7 @@
     <row r="272">
       <c r="A272" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="B272" s="14" t="inlineStr">
@@ -11073,7 +11073,7 @@
     <row r="273">
       <c r="A273" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="B273" s="14" t="inlineStr">
@@ -11102,7 +11102,7 @@
     <row r="274">
       <c r="A274" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="B274" s="14" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="G277" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
     </row>
@@ -11817,7 +11817,7 @@
     <row r="297">
       <c r="A297" s="14" t="inlineStr">
         <is>
-          <t>Integration Status as Admin_IntegrationStatus</t>
+          <t>Integration Status as Admin_Integration_Status</t>
         </is>
       </c>
       <c r="B297" s="14" t="inlineStr">
@@ -11850,7 +11850,7 @@
     <row r="298">
       <c r="A298" s="14" t="inlineStr">
         <is>
-          <t>Integration Status as Admin_IntegrationStatus</t>
+          <t>Integration Status as Admin_Integration_Status</t>
         </is>
       </c>
       <c r="B298" s="15" t="inlineStr">
@@ -11879,7 +11879,7 @@
     <row r="299">
       <c r="A299" s="14" t="inlineStr">
         <is>
-          <t>Integration Status as Admin_IntegrationStatus</t>
+          <t>Integration Status as Admin_Integration_Status</t>
         </is>
       </c>
       <c r="B299" s="14" t="inlineStr">
@@ -11908,7 +11908,7 @@
     <row r="300">
       <c r="A300" s="14" t="inlineStr">
         <is>
-          <t>Integration Status as Admin_IntegrationStatus</t>
+          <t>Integration Status as Admin_Integration_Status</t>
         </is>
       </c>
       <c r="B300" s="14" t="inlineStr">
@@ -11937,7 +11937,7 @@
     <row r="301">
       <c r="A301" s="14" t="inlineStr">
         <is>
-          <t>Integration Status as Admin_IntegrationStatus</t>
+          <t>Integration Status as Admin_Integration_Status</t>
         </is>
       </c>
       <c r="B301" s="15" t="inlineStr">
@@ -11966,7 +11966,7 @@
     <row r="302">
       <c r="A302" s="14" t="inlineStr">
         <is>
-          <t>Integration Status as Admin_IntegrationStatus</t>
+          <t>Integration Status as Admin_Integration_Status</t>
         </is>
       </c>
       <c r="B302" s="14" t="inlineStr">
@@ -11995,7 +11995,7 @@
     <row r="303">
       <c r="A303" s="14" t="inlineStr">
         <is>
-          <t>Integration Status as Admin_IntegrationStatus</t>
+          <t>Integration Status as Admin_Integration_Status</t>
         </is>
       </c>
       <c r="B303" s="14" t="inlineStr">
@@ -12024,7 +12024,7 @@
     <row r="304">
       <c r="A304" s="14" t="inlineStr">
         <is>
-          <t>Integration Status as Admin_IntegrationStatus</t>
+          <t>Integration Status as Admin_Integration_Status</t>
         </is>
       </c>
       <c r="B304" s="14" t="inlineStr">
@@ -12053,7 +12053,7 @@
     <row r="305">
       <c r="A305" s="14" t="inlineStr">
         <is>
-          <t>Integration Status as Admin_IntegrationStatus</t>
+          <t>Integration Status as Admin_Integration_Status</t>
         </is>
       </c>
       <c r="B305" s="14" t="inlineStr">
@@ -12082,7 +12082,7 @@
     <row r="306">
       <c r="A306" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B306" s="14" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="E306" s="14" t="inlineStr">
         <is>
-          <t>Unique number of each row in Integration Run Log as ClearOps_Logs</t>
+          <t>Unique number of each row in Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="F306" s="14" t="inlineStr">
@@ -12115,7 +12115,7 @@
     <row r="307">
       <c r="A307" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B307" s="14" t="inlineStr">
@@ -12145,14 +12145,14 @@
       </c>
       <c r="G307" s="14" t="inlineStr">
         <is>
-          <t>Integration Status as Admin_IntegrationStatus</t>
+          <t>Integration Status as Admin_Integration_Status</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B308" s="15" t="inlineStr">
@@ -12181,7 +12181,7 @@
     <row r="309">
       <c r="A309" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B309" s="16" t="inlineStr">
@@ -12210,7 +12210,7 @@
     <row r="310">
       <c r="A310" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B310" s="16" t="inlineStr">
@@ -12239,7 +12239,7 @@
     <row r="311">
       <c r="A311" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B311" s="16" t="inlineStr">
@@ -12268,7 +12268,7 @@
     <row r="312">
       <c r="A312" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B312" s="16" t="inlineStr">
@@ -12297,7 +12297,7 @@
     <row r="313">
       <c r="A313" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B313" s="16" t="inlineStr">
@@ -12326,7 +12326,7 @@
     <row r="314">
       <c r="A314" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B314" s="16" t="inlineStr">
@@ -12355,7 +12355,7 @@
     <row r="315">
       <c r="A315" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B315" s="16" t="inlineStr">
@@ -12384,7 +12384,7 @@
     <row r="316">
       <c r="A316" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B316" s="16" t="inlineStr">
@@ -12413,7 +12413,7 @@
     <row r="317">
       <c r="A317" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B317" s="16" t="inlineStr">
@@ -12549,7 +12549,7 @@
       <c r="D321" s="14" t="inlineStr"/>
       <c r="E321" s="14" t="inlineStr">
         <is>
-          <t>Active or inactive [From RolesandPermissions]</t>
+          <t>Active or inactive [From ClearOps_RolesandPermissions]</t>
         </is>
       </c>
       <c r="F321" s="14" t="inlineStr">
@@ -12785,7 +12785,7 @@
       <c r="D329" s="14" t="inlineStr"/>
       <c r="E329" s="14" t="inlineStr">
         <is>
-          <t>Group of pages [Moved from RolesandPermissions]</t>
+          <t>Group of pages [Moved from ClearOps_RolesandPermissions]</t>
         </is>
       </c>
       <c r="F329" s="14" t="inlineStr">
@@ -12914,7 +12914,7 @@
     <row r="334">
       <c r="A334" s="14" t="inlineStr">
         <is>
-          <t>Access Levels as ClearOps_Access</t>
+          <t>Access Levels as ClearOpps_Access_table</t>
         </is>
       </c>
       <c r="B334" s="14" t="inlineStr">
@@ -12947,7 +12947,7 @@
     <row r="335">
       <c r="A335" s="14" t="inlineStr">
         <is>
-          <t>Access Levels as ClearOps_Access</t>
+          <t>Access Levels as ClearOpps_Access_table</t>
         </is>
       </c>
       <c r="B335" s="15" t="inlineStr">
@@ -12976,7 +12976,7 @@
     <row r="336">
       <c r="A336" s="14" t="inlineStr">
         <is>
-          <t>Access Levels as ClearOps_Access</t>
+          <t>Access Levels as ClearOpps_Access_table</t>
         </is>
       </c>
       <c r="B336" s="14" t="inlineStr">
@@ -13005,7 +13005,7 @@
     <row r="337">
       <c r="A337" s="14" t="inlineStr">
         <is>
-          <t>Access Levels as ClearOps_Access</t>
+          <t>Access Levels as ClearOpps_Access_table</t>
         </is>
       </c>
       <c r="B337" s="14" t="inlineStr">
@@ -13034,7 +13034,7 @@
     <row r="338">
       <c r="A338" s="14" t="inlineStr">
         <is>
-          <t>Access Levels as ClearOps_Access</t>
+          <t>Access Levels as ClearOpps_Access_table</t>
         </is>
       </c>
       <c r="B338" s="14" t="inlineStr">
@@ -13063,7 +13063,7 @@
     <row r="339">
       <c r="A339" s="14" t="inlineStr">
         <is>
-          <t>Access Levels as ClearOps_Access</t>
+          <t>Access Levels as ClearOpps_Access_table</t>
         </is>
       </c>
       <c r="B339" s="14" t="inlineStr">
@@ -13229,7 +13229,7 @@
       </c>
       <c r="G343" s="14" t="inlineStr">
         <is>
-          <t>Access Levels as ClearOps_Access</t>
+          <t>Access Levels as ClearOpps_Access_table</t>
         </is>
       </c>
     </row>
@@ -13604,7 +13604,7 @@
     <row r="356">
       <c r="A356" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link as ClearOps_Login</t>
+          <t>Single Sign-On Link as ClearOps_login</t>
         </is>
       </c>
       <c r="B356" s="16" t="inlineStr">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="E356" s="14" t="inlineStr">
         <is>
-          <t>Unique number of each row in Single Sign-On Link as ClearOps_Login [Was missing – table had no PK]</t>
+          <t>Unique number of each row in Single Sign-On Link as ClearOps_login [Was missing – table had no PK]</t>
         </is>
       </c>
       <c r="F356" s="14" t="inlineStr">
@@ -13637,7 +13637,7 @@
     <row r="357">
       <c r="A357" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link as ClearOps_Login</t>
+          <t>Single Sign-On Link as ClearOps_login</t>
         </is>
       </c>
       <c r="B357" s="14" t="inlineStr">
@@ -13674,7 +13674,7 @@
     <row r="358">
       <c r="A358" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link as ClearOps_Login</t>
+          <t>Single Sign-On Link as ClearOps_login</t>
         </is>
       </c>
       <c r="B358" s="15" t="inlineStr">
@@ -13703,7 +13703,7 @@
     <row r="359">
       <c r="A359" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link as ClearOps_Login</t>
+          <t>Single Sign-On Link as ClearOps_login</t>
         </is>
       </c>
       <c r="B359" s="14" t="inlineStr">
@@ -13732,7 +13732,7 @@
     <row r="360">
       <c r="A360" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link as ClearOps_Login</t>
+          <t>Single Sign-On Link as ClearOps_login</t>
         </is>
       </c>
       <c r="B360" s="14" t="inlineStr">
@@ -13761,7 +13761,7 @@
     <row r="361">
       <c r="A361" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link as ClearOps_Login</t>
+          <t>Single Sign-On Link as ClearOps_login</t>
         </is>
       </c>
       <c r="B361" s="14" t="inlineStr">
@@ -13790,7 +13790,7 @@
     <row r="362">
       <c r="A362" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link as ClearOps_Login</t>
+          <t>Single Sign-On Link as ClearOps_login</t>
         </is>
       </c>
       <c r="B362" s="14" t="inlineStr">
@@ -13819,7 +13819,7 @@
     <row r="363">
       <c r="A363" s="14" t="inlineStr">
         <is>
-          <t>Login History as ClearOps_UserLogin</t>
+          <t>Login History as UserLogin</t>
         </is>
       </c>
       <c r="B363" s="16" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="E363" s="14" t="inlineStr">
         <is>
-          <t>Unique number of each row in Login History as ClearOps_UserLogin [Was missing – no PK]</t>
+          <t>Unique number of each row in Login History as UserLogin [Was missing – no PK]</t>
         </is>
       </c>
       <c r="F363" s="14" t="inlineStr">
@@ -13852,7 +13852,7 @@
     <row r="364">
       <c r="A364" s="14" t="inlineStr">
         <is>
-          <t>Login History as ClearOps_UserLogin</t>
+          <t>Login History as UserLogin</t>
         </is>
       </c>
       <c r="B364" s="14" t="inlineStr">
@@ -13889,7 +13889,7 @@
     <row r="365">
       <c r="A365" s="14" t="inlineStr">
         <is>
-          <t>Login History as ClearOps_UserLogin</t>
+          <t>Login History as UserLogin</t>
         </is>
       </c>
       <c r="B365" s="15" t="inlineStr">
@@ -13918,7 +13918,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Login History as ClearOps_UserLogin</t>
+          <t>Login History as UserLogin</t>
         </is>
       </c>
       <c r="B366" s="14" t="inlineStr">
@@ -14307,7 +14307,7 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>Each Pass-through Costs as ClearOps_Passthrough row points to one Project Tasks (WBS) as ClearOps_ProjectWBS row</t>
+          <t>Each Pass-through Costs as ClearOps_Passthrough row points to one Project Tasks (WBS) as ProjectWBS row</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -14550,12 +14550,12 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>Each Time Off as ClearOps_TimeOff row points to one People (HR master list) as Employee_Master row</t>
+          <t>Each Time Off as TimeOff(WD) row points to one People (HR master list) as Employee_Master row</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>Time Off as ClearOps_TimeOff</t>
+          <t>Time Off as TimeOff(WD)</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
@@ -14577,12 +14577,12 @@
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>Each Time Planner as ClearOps_ProjectTimePlanner row points to one Projects as Project_Master row</t>
+          <t>Each Time Planner as ClearOps_Project_Time_Planner row points to one Projects as Project_Master row</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
@@ -14604,12 +14604,12 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>Each Time Planner as ClearOps_ProjectTimePlanner row points to one Project Tasks (WBS) as ClearOps_ProjectWBS row</t>
+          <t>Each Time Planner as ClearOps_Project_Time_Planner row points to one Project Tasks (WBS) as ProjectWBS row</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="E26" s="16" t="inlineStr">
@@ -14631,12 +14631,12 @@
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Each Time Planner as ClearOps_ProjectTimePlanner row points to one Resources (bookable people) as Resources row</t>
+          <t>Each Time Planner as ClearOps_Project_Time_Planner row points to one Resources (bookable people) as Resources row</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
@@ -14928,12 +14928,12 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Each Project Tasks (WBS) as ClearOps_ProjectWBS row points to one Projects as Project_Master row</t>
+          <t>Each Project Tasks (WBS) as ProjectWBS row points to one Projects as Project_Master row</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
@@ -14955,12 +14955,12 @@
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>Each Project Tasks (WBS) as ClearOps_ProjectWBS row points to one Project Tasks (WBS) as ClearOps_ProjectWBS row</t>
+          <t>Each Project Tasks (WBS) as ProjectWBS row points to one Project Tasks (WBS) as ProjectWBS row</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -14982,12 +14982,12 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Each Project Tasks (WBS) as ClearOps_ProjectWBS row points to one Project Tasks (WBS) as ClearOps_ProjectWBS row</t>
+          <t>Each Project Tasks (WBS) as ProjectWBS row points to one Project Tasks (WBS) as ProjectWBS row</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="E40" s="16" t="inlineStr">
@@ -15009,12 +15009,12 @@
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Each Project Estimates as ClearOps_ProjectEstimator row points to one Projects as Project_Master row</t>
+          <t>Each Project Estimates as Project_Estimator row points to one Projects as Project_Master row</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="C41" s="14" t="inlineStr">
@@ -15036,12 +15036,12 @@
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>Each Project Estimates as ClearOps_ProjectEstimator row points to one Project Tasks (WBS) as ClearOps_ProjectWBS row</t>
+          <t>Each Project Estimates as Project_Estimator row points to one Project Tasks (WBS) as ProjectWBS row</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="E42" s="16" t="inlineStr">
@@ -15063,12 +15063,12 @@
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>Each Project Estimates as ClearOps_ProjectEstimator row points to one Job Grades as Grades row</t>
+          <t>Each Project Estimates as Project_Estimator row points to one Job Grades as Grades row</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
@@ -15090,12 +15090,12 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>Each Project Finance Settings as ClearOps_ProjectSettings row points to one Projects as Project_Master row</t>
+          <t>Each Project Finance Settings as Project_Settings row points to one Projects as Project_Master row</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
@@ -15144,7 +15144,7 @@
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Each Project Assignments (grid rows) as ClearOps_ProjectSTP row points to one Project Tasks (WBS) as ClearOps_ProjectWBS row</t>
+          <t>Each Project Assignments (grid rows) as ClearOps_ProjectSTP row points to one Project Tasks (WBS) as ProjectWBS row</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="E46" s="16" t="inlineStr">
@@ -15252,12 +15252,12 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>Each Integration Run Log as ClearOps_Logs row points to one Integration Status as Admin_IntegrationStatus row</t>
+          <t>Each Integration Run Log as Logs_table row points to one Integration Status as Admin_Integration_Status row</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>Integration Status as Admin_IntegrationStatus</t>
+          <t>Integration Status as Admin_Integration_Status</t>
         </is>
       </c>
       <c r="E50" s="16" t="inlineStr">
@@ -15333,7 +15333,7 @@
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>Each Permissions as ClearOps_Permission row points to one Access Levels as ClearOps_Access row</t>
+          <t>Each Permissions as ClearOps_Permission row points to one Access Levels as ClearOpps_Access_table row</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
@@ -15348,7 +15348,7 @@
       </c>
       <c r="D53" s="14" t="inlineStr">
         <is>
-          <t>Access Levels as ClearOps_Access</t>
+          <t>Access Levels as ClearOpps_Access_table</t>
         </is>
       </c>
       <c r="E53" s="16" t="inlineStr">
@@ -15414,12 +15414,12 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>Each Single Sign-On Link as ClearOps_Login row points to one People (HR master list) as Employee_Master row</t>
+          <t>Each Single Sign-On Link as ClearOps_login row points to one People (HR master list) as Employee_Master row</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link as ClearOps_Login</t>
+          <t>Single Sign-On Link as ClearOps_login</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
@@ -15441,12 +15441,12 @@
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
-          <t>Each Login History as ClearOps_UserLogin row points to one Application Users as ClearOps_Users row</t>
+          <t>Each Login History as UserLogin row points to one Application Users as ClearOps_Users row</t>
         </is>
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Login History as ClearOps_UserLogin</t>
+          <t>Login History as UserLogin</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
@@ -16876,7 +16876,7 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>Time Off as ClearOps_TimeOff</t>
+          <t>Time Off as TimeOff(WD)</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
@@ -16898,7 +16898,7 @@
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>Time Off as ClearOps_TimeOff</t>
+          <t>Time Off as TimeOff(WD)</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
@@ -16920,7 +16920,7 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Time Off as ClearOps_TimeOff</t>
+          <t>Time Off as TimeOff(WD)</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
@@ -16942,7 +16942,7 @@
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
@@ -16964,7 +16964,7 @@
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>Time Planner as ClearOps_ProjectTimePlanner</t>
+          <t>Time Planner as ClearOps_Project_Time_Planner</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
@@ -17140,7 +17140,7 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
@@ -17162,7 +17162,7 @@
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
@@ -17184,7 +17184,7 @@
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
@@ -17206,7 +17206,7 @@
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
@@ -17228,7 +17228,7 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
@@ -17250,7 +17250,7 @@
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>Project Tasks (WBS) as ClearOps_ProjectWBS</t>
+          <t>Project Tasks (WBS) as ProjectWBS</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
@@ -17272,7 +17272,7 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
@@ -17294,7 +17294,7 @@
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
@@ -17316,7 +17316,7 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>Project Estimates as ClearOps_ProjectEstimator</t>
+          <t>Project Estimates as Project_Estimator</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
@@ -17338,7 +17338,7 @@
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
@@ -17360,7 +17360,7 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Project Finance Settings as ClearOps_ProjectSettings</t>
+          <t>Project Finance Settings as Project_Settings</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
@@ -17558,7 +17558,7 @@
     <row r="63">
       <c r="A63" s="14" t="inlineStr">
         <is>
-          <t>Project Forecasting (OLD) as ClearOps_ProjectForecasting</t>
+          <t>Project Forecasting (OLD) as Project_Forecasting</t>
         </is>
       </c>
       <c r="B63" s="14" t="inlineStr">
@@ -17580,7 +17580,7 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>Integration Status as Admin_IntegrationStatus</t>
+          <t>Integration Status as Admin_Integration_Status</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
@@ -17602,7 +17602,7 @@
     <row r="65">
       <c r="A65" s="14" t="inlineStr">
         <is>
-          <t>Integration Status as Admin_IntegrationStatus</t>
+          <t>Integration Status as Admin_Integration_Status</t>
         </is>
       </c>
       <c r="B65" s="14" t="inlineStr">
@@ -17624,7 +17624,7 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
@@ -17646,7 +17646,7 @@
     <row r="67">
       <c r="A67" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B67" s="14" t="inlineStr">
@@ -17668,7 +17668,7 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
@@ -17690,7 +17690,7 @@
     <row r="69">
       <c r="A69" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B69" s="14" t="inlineStr">
@@ -17712,7 +17712,7 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
@@ -17734,7 +17734,7 @@
     <row r="71">
       <c r="A71" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B71" s="14" t="inlineStr">
@@ -17756,7 +17756,7 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
@@ -17778,7 +17778,7 @@
     <row r="73">
       <c r="A73" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B73" s="14" t="inlineStr">
@@ -17800,7 +17800,7 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
@@ -17822,7 +17822,7 @@
     <row r="75">
       <c r="A75" s="14" t="inlineStr">
         <is>
-          <t>Integration Run Log as ClearOps_Logs</t>
+          <t>Integration Run Log as Logs_table</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>From RolesandPermissions</t>
+          <t>From ClearOps_RolesandPermissions</t>
         </is>
       </c>
     </row>
@@ -17881,14 +17881,14 @@
       </c>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>Moved from RolesandPermissions</t>
+          <t>Moved from ClearOps_RolesandPermissions</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>Access Levels as ClearOps_Access</t>
+          <t>Access Levels as ClearOpps_Access_table</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
@@ -17976,7 +17976,7 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link as ClearOps_Login</t>
+          <t>Single Sign-On Link as ClearOps_login</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
@@ -17998,7 +17998,7 @@
     <row r="83">
       <c r="A83" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link as ClearOps_Login</t>
+          <t>Single Sign-On Link as ClearOps_login</t>
         </is>
       </c>
       <c r="B83" s="14" t="inlineStr">
@@ -18020,7 +18020,7 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>Single Sign-On Link as ClearOps_Login</t>
+          <t>Single Sign-On Link as ClearOps_login</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
@@ -18042,7 +18042,7 @@
     <row r="85">
       <c r="A85" s="14" t="inlineStr">
         <is>
-          <t>Login History as ClearOps_UserLogin</t>
+          <t>Login History as UserLogin</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
@@ -18064,7 +18064,7 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>Login History as ClearOps_UserLogin</t>
+          <t>Login History as UserLogin</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
@@ -18086,7 +18086,7 @@
     <row r="87">
       <c r="A87" s="14" t="inlineStr">
         <is>
-          <t>Login History as ClearOps_UserLogin</t>
+          <t>Login History as UserLogin</t>
         </is>
       </c>
       <c r="B87" s="14" t="inlineStr">
@@ -18108,7 +18108,7 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>Roles &amp; Permissions (OLD sheet) as RolesandPermissions</t>
+          <t>Roles &amp; Permissions (OLD sheet) as ClearOps_RolesandPermissions</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">

--- a/ClearOps_Database_Mapped.xlsx
+++ b/ClearOps_Database_Mapped.xlsx
@@ -1458,7 +1458,7 @@
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>Login History as UserLogin</t>
+          <t>Login History as User_Login</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Login History as UserLogin</t>
+          <t>Login History as User_Login</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>UserLogin</t>
+          <t>User_Login</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -13819,7 +13819,7 @@
     <row r="363">
       <c r="A363" s="14" t="inlineStr">
         <is>
-          <t>Login History as UserLogin</t>
+          <t>Login History as User_Login</t>
         </is>
       </c>
       <c r="B363" s="16" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="E363" s="14" t="inlineStr">
         <is>
-          <t>Unique number of each row in Login History as UserLogin [Was missing – no PK]</t>
+          <t>Unique number of each row in Login History as User_Login [Was missing – no PK]</t>
         </is>
       </c>
       <c r="F363" s="14" t="inlineStr">
@@ -13852,7 +13852,7 @@
     <row r="364">
       <c r="A364" s="14" t="inlineStr">
         <is>
-          <t>Login History as UserLogin</t>
+          <t>Login History as User_Login</t>
         </is>
       </c>
       <c r="B364" s="14" t="inlineStr">
@@ -13889,7 +13889,7 @@
     <row r="365">
       <c r="A365" s="14" t="inlineStr">
         <is>
-          <t>Login History as UserLogin</t>
+          <t>Login History as User_Login</t>
         </is>
       </c>
       <c r="B365" s="15" t="inlineStr">
@@ -13918,7 +13918,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Login History as UserLogin</t>
+          <t>Login History as User_Login</t>
         </is>
       </c>
       <c r="B366" s="14" t="inlineStr">
@@ -15441,12 +15441,12 @@
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
-          <t>Each Login History as UserLogin row points to one Application Users as ClearOps_Users row</t>
+          <t>Each Login History as User_Login row points to one Application Users as ClearOps_Users row</t>
         </is>
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Login History as UserLogin</t>
+          <t>Login History as User_Login</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
@@ -18042,7 +18042,7 @@
     <row r="85">
       <c r="A85" s="14" t="inlineStr">
         <is>
-          <t>Login History as UserLogin</t>
+          <t>Login History as User_Login</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
@@ -18064,7 +18064,7 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>Login History as UserLogin</t>
+          <t>Login History as User_Login</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
@@ -18086,7 +18086,7 @@
     <row r="87">
       <c r="A87" s="14" t="inlineStr">
         <is>
-          <t>Login History as UserLogin</t>
+          <t>Login History as User_Login</t>
         </is>
       </c>
       <c r="B87" s="14" t="inlineStr">
